--- a/artfynd/A 48749-2025 artfynd.xlsx
+++ b/artfynd/A 48749-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129671611</v>
       </c>
       <c r="B2" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>129671679</v>
       </c>
       <c r="B3" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>129671353</v>
       </c>
       <c r="B4" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,42 +997,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129671369</v>
+        <v>129671604</v>
       </c>
       <c r="B5" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>781313</v>
+        <v>781583</v>
       </c>
       <c r="R5" t="n">
-        <v>7143250</v>
+        <v>7143145</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1070,17 +1070,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ca 1 x 3 meter med bladrosetter!</t>
+          <t>hack i låga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1089,7 +1089,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1108,42 +1107,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129671604</v>
+        <v>129671369</v>
       </c>
       <c r="B6" t="n">
-        <v>57724</v>
+        <v>98756</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1151,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>781583</v>
+        <v>781313</v>
       </c>
       <c r="R6" t="n">
-        <v>7143145</v>
+        <v>7143250</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,17 +1180,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>hack i låga</t>
+          <t>ca 1 x 3 meter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,6 +1199,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1221,7 +1221,7 @@
         <v>129671322</v>
       </c>
       <c r="B7" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>129671307</v>
       </c>
       <c r="B8" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>129670173</v>
       </c>
       <c r="B9" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>129671431</v>
       </c>
       <c r="B10" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1654,41 +1654,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129671725</v>
+        <v>129671399</v>
       </c>
       <c r="B11" t="n">
-        <v>91553</v>
+        <v>98756</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1696,10 +1701,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>781721</v>
+        <v>781522</v>
       </c>
       <c r="R11" t="n">
-        <v>7143412</v>
+        <v>7143269</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1726,12 +1731,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>med överblommad blomstängel</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1759,46 +1769,41 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129671399</v>
+        <v>129671725</v>
       </c>
       <c r="B12" t="n">
-        <v>98727</v>
+        <v>91581</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1806,10 +1811,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>781522</v>
+        <v>781721</v>
       </c>
       <c r="R12" t="n">
-        <v>7143269</v>
+        <v>7143412</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1836,17 +1841,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>med överblommad blomstängel</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1874,38 +1874,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129671776</v>
+        <v>129670107</v>
       </c>
       <c r="B13" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1913,10 +1917,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>781537</v>
+        <v>781364</v>
       </c>
       <c r="R13" t="n">
-        <v>7143351</v>
+        <v>7143210</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1943,17 +1947,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ca 2 x 1 m med bladrosetter</t>
+          <t>hål i naturlig granstubbe</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1962,7 +1966,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1984,7 +1987,7 @@
         <v>129670229</v>
       </c>
       <c r="B14" t="n">
-        <v>91851</v>
+        <v>91879</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2091,10 +2094,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129670096</v>
+        <v>129671776</v>
       </c>
       <c r="B15" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2120,11 +2123,7 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -2134,10 +2133,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>781314</v>
+        <v>781537</v>
       </c>
       <c r="R15" t="n">
-        <v>7143242</v>
+        <v>7143351</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2164,17 +2163,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ca 1x1 meter med bladrosetter</t>
+          <t>ca 2 x 1 m med bladrosetter</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2202,42 +2201,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129670107</v>
+        <v>129670096</v>
       </c>
       <c r="B16" t="n">
-        <v>57724</v>
+        <v>98756</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2245,10 +2244,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>781364</v>
+        <v>781314</v>
       </c>
       <c r="R16" t="n">
-        <v>7143210</v>
+        <v>7143242</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2285,7 +2284,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>hål i naturlig granstubbe</t>
+          <t>ca 1x1 meter med bladrosetter</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2294,6 +2293,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2315,7 +2315,7 @@
         <v>129671733</v>
       </c>
       <c r="B17" t="n">
-        <v>82878</v>
+        <v>82905</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>129671643</v>
       </c>
       <c r="B18" t="n">
-        <v>91504</v>
+        <v>91532</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>129671583</v>
       </c>
       <c r="B19" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129671522</v>
+        <v>129671437</v>
       </c>
       <c r="B20" t="n">
-        <v>57724</v>
+        <v>82905</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2643,31 +2643,30 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2675,10 +2674,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>781374</v>
+        <v>781567</v>
       </c>
       <c r="R20" t="n">
-        <v>7143326</v>
+        <v>7143316</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2715,7 +2714,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>färska hål i gran</t>
+          <t>på krokig gammelgran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2724,6 +2723,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2742,32 +2742,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129671769</v>
+        <v>129671717</v>
       </c>
       <c r="B21" t="n">
-        <v>91517</v>
+        <v>91581</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2784,10 +2784,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>781492</v>
+        <v>781823</v>
       </c>
       <c r="R21" t="n">
-        <v>7143441</v>
+        <v>7143286</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2847,32 +2847,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129671437</v>
+        <v>129671769</v>
       </c>
       <c r="B22" t="n">
-        <v>82878</v>
+        <v>91545</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>781567</v>
+        <v>781492</v>
       </c>
       <c r="R22" t="n">
-        <v>7143316</v>
+        <v>7143441</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2919,17 +2919,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>på krokig gammelgran</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2957,42 +2952,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129671688</v>
+        <v>129671522</v>
       </c>
       <c r="B23" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3000,10 +2995,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>781774</v>
+        <v>781374</v>
       </c>
       <c r="R23" t="n">
-        <v>7143251</v>
+        <v>7143326</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3030,17 +3025,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>3 x 1 meter med bladrosetter!</t>
+          <t>färska hål i gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3049,7 +3044,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3068,41 +3062,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129671717</v>
+        <v>129671688</v>
       </c>
       <c r="B24" t="n">
-        <v>91553</v>
+        <v>98756</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3110,10 +3105,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>781823</v>
+        <v>781774</v>
       </c>
       <c r="R24" t="n">
-        <v>7143286</v>
+        <v>7143251</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3146,6 +3141,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>3 x 1 meter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3176,7 +3176,7 @@
         <v>129671328</v>
       </c>
       <c r="B25" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3284,41 +3284,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129671363</v>
+        <v>129671422</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>98756</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3326,10 +3327,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>781284</v>
+        <v>781559</v>
       </c>
       <c r="R26" t="n">
-        <v>7143261</v>
+        <v>7143298</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3362,6 +3363,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>ca 2 x 2 meter med bladrosetter</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3389,42 +3395,41 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129671422</v>
+        <v>129671363</v>
       </c>
       <c r="B27" t="n">
-        <v>98727</v>
+        <v>79070</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3432,10 +3437,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>781559</v>
+        <v>781284</v>
       </c>
       <c r="R27" t="n">
-        <v>7143298</v>
+        <v>7143261</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3468,11 +3473,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>ca 2 x 2 meter med bladrosetter</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3503,7 +3503,7 @@
         <v>129671572</v>
       </c>
       <c r="B28" t="n">
-        <v>91573</v>
+        <v>91601</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         <v>129671659</v>
       </c>
       <c r="B29" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129671632</v>
+        <v>129671514</v>
       </c>
       <c r="B30" t="n">
         <v>57727</v>
@@ -3718,16 +3718,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3738,7 +3738,11 @@
       <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3746,10 +3750,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>781623</v>
+        <v>781563</v>
       </c>
       <c r="R30" t="n">
-        <v>7143270</v>
+        <v>7143446</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3776,17 +3780,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>gammalt bohål i granlåga, rätt storlek för tretåig hackspett</t>
+          <t>färska hål</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3813,10 +3817,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129671514</v>
+        <v>129671632</v>
       </c>
       <c r="B31" t="n">
-        <v>57724</v>
+        <v>57730</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3824,16 +3828,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3844,11 +3848,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3856,10 +3856,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>781563</v>
+        <v>781623</v>
       </c>
       <c r="R31" t="n">
-        <v>7143446</v>
+        <v>7143270</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3886,17 +3886,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>färska hål</t>
+          <t>gammalt bohål i granlåga, rätt storlek för tretåig hackspett</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3926,7 +3926,7 @@
         <v>129671647</v>
       </c>
       <c r="B32" t="n">
-        <v>82878</v>
+        <v>82905</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>129671752</v>
       </c>
       <c r="B33" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4137,7 +4137,7 @@
         <v>129671316</v>
       </c>
       <c r="B34" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4244,10 +4244,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129671452</v>
+        <v>129670180</v>
       </c>
       <c r="B35" t="n">
-        <v>98727</v>
+        <v>91963</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4255,31 +4255,30 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>1506</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4287,10 +4286,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>781558</v>
+        <v>781534</v>
       </c>
       <c r="R35" t="n">
-        <v>7143348</v>
+        <v>7143302</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4323,6 +4322,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>på granlåga med ullticka, kötticka och rosenticka</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4350,10 +4354,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129670180</v>
+        <v>129671452</v>
       </c>
       <c r="B36" t="n">
-        <v>91935</v>
+        <v>98756</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4361,30 +4365,31 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1506</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4392,10 +4397,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>781534</v>
+        <v>781558</v>
       </c>
       <c r="R36" t="n">
-        <v>7143302</v>
+        <v>7143348</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4428,11 +4433,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>på granlåga med ullticka, kötticka och rosenticka</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 48749-2025 artfynd.xlsx
+++ b/artfynd/A 48749-2025 artfynd.xlsx
@@ -2632,10 +2632,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129671437</v>
+        <v>129671522</v>
       </c>
       <c r="B20" t="n">
-        <v>82905</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2643,30 +2643,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2674,10 +2675,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>781567</v>
+        <v>781374</v>
       </c>
       <c r="R20" t="n">
-        <v>7143316</v>
+        <v>7143326</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2714,7 +2715,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>på krokig gammelgran</t>
+          <t>färska hål i gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2723,7 +2724,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2742,32 +2742,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129671717</v>
+        <v>129671769</v>
       </c>
       <c r="B21" t="n">
-        <v>91581</v>
+        <v>91545</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2784,10 +2784,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>781823</v>
+        <v>781492</v>
       </c>
       <c r="R21" t="n">
-        <v>7143286</v>
+        <v>7143441</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2847,41 +2847,42 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129671769</v>
+        <v>129671688</v>
       </c>
       <c r="B22" t="n">
-        <v>91545</v>
+        <v>98756</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2889,10 +2890,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>781492</v>
+        <v>781774</v>
       </c>
       <c r="R22" t="n">
-        <v>7143441</v>
+        <v>7143251</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2925,6 +2926,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>3 x 1 meter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2952,10 +2958,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129671522</v>
+        <v>129671437</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>82905</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2963,31 +2969,30 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2995,10 +3000,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>781374</v>
+        <v>781567</v>
       </c>
       <c r="R23" t="n">
-        <v>7143326</v>
+        <v>7143316</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3035,7 +3040,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>färska hål i gran</t>
+          <t>på krokig gammelgran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3044,6 +3049,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3062,42 +3068,41 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129671688</v>
+        <v>129671717</v>
       </c>
       <c r="B24" t="n">
-        <v>98756</v>
+        <v>91581</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3105,10 +3110,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>781774</v>
+        <v>781823</v>
       </c>
       <c r="R24" t="n">
-        <v>7143251</v>
+        <v>7143286</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3141,11 +3146,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>3 x 1 meter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 48749-2025 artfynd.xlsx
+++ b/artfynd/A 48749-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129671611</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>129671679</v>
       </c>
       <c r="B3" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>129671353</v>
       </c>
       <c r="B4" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,42 +997,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129671604</v>
+        <v>129671369</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>98768</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>781583</v>
+        <v>781313</v>
       </c>
       <c r="R5" t="n">
-        <v>7143145</v>
+        <v>7143250</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1070,17 +1070,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>hack i låga</t>
+          <t>ca 1 x 3 meter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1089,6 +1089,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1107,42 +1108,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129671369</v>
+        <v>129671604</v>
       </c>
       <c r="B6" t="n">
-        <v>98756</v>
+        <v>57732</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1150,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>781313</v>
+        <v>781583</v>
       </c>
       <c r="R6" t="n">
-        <v>7143250</v>
+        <v>7143145</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,17 +1181,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ca 1 x 3 meter med bladrosetter!</t>
+          <t>hack i låga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1199,7 +1200,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1221,7 +1221,7 @@
         <v>129671322</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>129671307</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>129670173</v>
       </c>
       <c r="B9" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,42 +1548,41 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129671431</v>
+        <v>129671725</v>
       </c>
       <c r="B10" t="n">
-        <v>98756</v>
+        <v>91587</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1591,10 +1590,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>781554</v>
+        <v>781721</v>
       </c>
       <c r="R10" t="n">
-        <v>7143299</v>
+        <v>7143412</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1621,12 +1620,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1654,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129671399</v>
+        <v>129671431</v>
       </c>
       <c r="B11" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,11 +1687,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1701,10 +1696,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>781522</v>
+        <v>781554</v>
       </c>
       <c r="R11" t="n">
-        <v>7143269</v>
+        <v>7143299</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1737,11 +1732,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>med överblommad blomstängel</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1769,41 +1759,46 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129671725</v>
+        <v>129671399</v>
       </c>
       <c r="B12" t="n">
-        <v>91581</v>
+        <v>98768</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1811,10 +1806,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>781721</v>
+        <v>781522</v>
       </c>
       <c r="R12" t="n">
-        <v>7143412</v>
+        <v>7143269</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,12 +1836,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>med överblommad blomstängel</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1874,10 +1874,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129670107</v>
+        <v>129670229</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>91885</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1885,31 +1885,30 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1917,10 +1916,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>781364</v>
+        <v>781534</v>
       </c>
       <c r="R13" t="n">
-        <v>7143210</v>
+        <v>7143302</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1957,7 +1956,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>hål i naturlig granstubbe</t>
+          <t>på samma låga som ostticka, kötticka och ullticka</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1966,6 +1965,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1984,10 +1984,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129670229</v>
+        <v>129670107</v>
       </c>
       <c r="B14" t="n">
-        <v>91879</v>
+        <v>57732</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1995,30 +1995,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2026,10 +2027,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>781534</v>
+        <v>781364</v>
       </c>
       <c r="R14" t="n">
-        <v>7143302</v>
+        <v>7143210</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2066,7 +2067,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>på samma låga som ostticka, kötticka och ullticka</t>
+          <t>hål i naturlig granstubbe</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2075,7 +2076,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2097,7 +2097,7 @@
         <v>129671776</v>
       </c>
       <c r="B15" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>129670096</v>
       </c>
       <c r="B16" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>129671733</v>
       </c>
       <c r="B17" t="n">
-        <v>82905</v>
+        <v>82910</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>129671643</v>
       </c>
       <c r="B18" t="n">
-        <v>91532</v>
+        <v>91538</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>129671583</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>129671522</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2742,41 +2742,42 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129671769</v>
+        <v>129671688</v>
       </c>
       <c r="B21" t="n">
-        <v>91545</v>
+        <v>98768</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2784,10 +2785,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>781492</v>
+        <v>781774</v>
       </c>
       <c r="R21" t="n">
-        <v>7143441</v>
+        <v>7143251</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2820,6 +2821,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>3 x 1 meter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2847,42 +2853,41 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129671688</v>
+        <v>129671769</v>
       </c>
       <c r="B22" t="n">
-        <v>98756</v>
+        <v>91551</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2890,10 +2895,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>781774</v>
+        <v>781492</v>
       </c>
       <c r="R22" t="n">
-        <v>7143251</v>
+        <v>7143441</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2926,11 +2931,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>3 x 1 meter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2961,7 +2961,7 @@
         <v>129671437</v>
       </c>
       <c r="B23" t="n">
-        <v>82905</v>
+        <v>82910</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>129671717</v>
       </c>
       <c r="B24" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3173,42 +3173,41 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129671328</v>
+        <v>129671363</v>
       </c>
       <c r="B25" t="n">
-        <v>98756</v>
+        <v>79075</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3216,10 +3215,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>781377</v>
+        <v>781284</v>
       </c>
       <c r="R25" t="n">
-        <v>7143460</v>
+        <v>7143261</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3252,11 +3251,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>ca 1 x 1 meter med bladrosetter</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3284,10 +3278,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129671422</v>
+        <v>129671328</v>
       </c>
       <c r="B26" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3327,10 +3321,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>781559</v>
+        <v>781377</v>
       </c>
       <c r="R26" t="n">
-        <v>7143298</v>
+        <v>7143460</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3367,7 +3361,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>ca 2 x 2 meter med bladrosetter</t>
+          <t>ca 1 x 1 meter med bladrosetter</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3395,41 +3389,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129671363</v>
+        <v>129671422</v>
       </c>
       <c r="B27" t="n">
-        <v>79070</v>
+        <v>98768</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3437,10 +3432,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>781284</v>
+        <v>781559</v>
       </c>
       <c r="R27" t="n">
-        <v>7143261</v>
+        <v>7143298</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3473,6 +3468,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>ca 2 x 2 meter med bladrosetter</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3503,7 +3503,7 @@
         <v>129671572</v>
       </c>
       <c r="B28" t="n">
-        <v>91601</v>
+        <v>91607</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         <v>129671659</v>
       </c>
       <c r="B29" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         <v>129671514</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>129671632</v>
       </c>
       <c r="B31" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         <v>129671647</v>
       </c>
       <c r="B32" t="n">
-        <v>82905</v>
+        <v>82910</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>129671752</v>
       </c>
       <c r="B33" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4134,42 +4134,41 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129671316</v>
+        <v>129670180</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>91969</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>1506</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4177,10 +4176,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>781538</v>
+        <v>781534</v>
       </c>
       <c r="R34" t="n">
-        <v>7143358</v>
+        <v>7143302</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4217,7 +4216,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>hål i högstubbe</t>
+          <t>på granlåga med ullticka, kötticka och rosenticka</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4226,6 +4225,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4244,41 +4244,42 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129670180</v>
+        <v>129671316</v>
       </c>
       <c r="B35" t="n">
-        <v>91963</v>
+        <v>57732</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1506</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4286,10 +4287,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>781534</v>
+        <v>781538</v>
       </c>
       <c r="R35" t="n">
-        <v>7143302</v>
+        <v>7143358</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4326,7 +4327,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>på granlåga med ullticka, kötticka och rosenticka</t>
+          <t>hål i högstubbe</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4335,7 +4336,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4357,7 +4357,7 @@
         <v>129671452</v>
       </c>
       <c r="B36" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 48749-2025 artfynd.xlsx
+++ b/artfynd/A 48749-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129671611</v>
       </c>
       <c r="B2" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>129671679</v>
       </c>
       <c r="B3" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>129671353</v>
       </c>
       <c r="B4" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,42 +997,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129671369</v>
+        <v>129671604</v>
       </c>
       <c r="B5" t="n">
-        <v>98768</v>
+        <v>57733</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>781313</v>
+        <v>781583</v>
       </c>
       <c r="R5" t="n">
-        <v>7143250</v>
+        <v>7143145</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1070,17 +1070,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ca 1 x 3 meter med bladrosetter!</t>
+          <t>hack i låga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1089,7 +1089,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1108,42 +1107,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129671604</v>
+        <v>129671369</v>
       </c>
       <c r="B6" t="n">
-        <v>57732</v>
+        <v>98769</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1151,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>781583</v>
+        <v>781313</v>
       </c>
       <c r="R6" t="n">
-        <v>7143145</v>
+        <v>7143250</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,17 +1180,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>hack i låga</t>
+          <t>ca 1 x 3 meter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,6 +1199,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1221,7 +1221,7 @@
         <v>129671322</v>
       </c>
       <c r="B7" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>129671307</v>
       </c>
       <c r="B8" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>129670173</v>
       </c>
       <c r="B9" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,41 +1548,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129671725</v>
+        <v>129671431</v>
       </c>
       <c r="B10" t="n">
-        <v>91587</v>
+        <v>98769</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1590,10 +1591,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>781721</v>
+        <v>781554</v>
       </c>
       <c r="R10" t="n">
-        <v>7143412</v>
+        <v>7143299</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1620,12 +1621,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,10 +1654,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129671431</v>
+        <v>129671399</v>
       </c>
       <c r="B11" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1687,7 +1688,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1696,10 +1701,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>781554</v>
+        <v>781522</v>
       </c>
       <c r="R11" t="n">
-        <v>7143299</v>
+        <v>7143269</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1732,6 +1737,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>med överblommad blomstängel</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1759,46 +1769,41 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129671399</v>
+        <v>129671725</v>
       </c>
       <c r="B12" t="n">
-        <v>98768</v>
+        <v>91588</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1806,10 +1811,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>781522</v>
+        <v>781721</v>
       </c>
       <c r="R12" t="n">
-        <v>7143269</v>
+        <v>7143412</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1836,17 +1841,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>med överblommad blomstängel</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1877,7 +1877,7 @@
         <v>129670229</v>
       </c>
       <c r="B13" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1984,42 +1984,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129670107</v>
+        <v>129670096</v>
       </c>
       <c r="B14" t="n">
-        <v>57732</v>
+        <v>98769</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>781364</v>
+        <v>781314</v>
       </c>
       <c r="R14" t="n">
-        <v>7143210</v>
+        <v>7143242</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>hål i naturlig granstubbe</t>
+          <t>ca 1x1 meter med bladrosetter</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2076,6 +2076,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2094,38 +2095,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129671776</v>
+        <v>129670107</v>
       </c>
       <c r="B15" t="n">
-        <v>98768</v>
+        <v>57733</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2133,10 +2138,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>781537</v>
+        <v>781364</v>
       </c>
       <c r="R15" t="n">
-        <v>7143351</v>
+        <v>7143210</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2163,17 +2168,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ca 2 x 1 m med bladrosetter</t>
+          <t>hål i naturlig granstubbe</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2182,7 +2187,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2201,10 +2205,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129670096</v>
+        <v>129671776</v>
       </c>
       <c r="B16" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2230,11 +2234,7 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -2244,10 +2244,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>781314</v>
+        <v>781537</v>
       </c>
       <c r="R16" t="n">
-        <v>7143242</v>
+        <v>7143351</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2274,17 +2274,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ca 1x1 meter med bladrosetter</t>
+          <t>ca 2 x 1 m med bladrosetter</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2315,7 +2315,7 @@
         <v>129671733</v>
       </c>
       <c r="B17" t="n">
-        <v>82910</v>
+        <v>82911</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>129671643</v>
       </c>
       <c r="B18" t="n">
-        <v>91538</v>
+        <v>91539</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>129671583</v>
       </c>
       <c r="B19" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129671522</v>
+        <v>129671437</v>
       </c>
       <c r="B20" t="n">
-        <v>57732</v>
+        <v>82911</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2643,31 +2643,30 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2675,10 +2674,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>781374</v>
+        <v>781567</v>
       </c>
       <c r="R20" t="n">
-        <v>7143326</v>
+        <v>7143316</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2715,7 +2714,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>färska hål i gran</t>
+          <t>på krokig gammelgran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2724,6 +2723,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2742,42 +2742,41 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129671688</v>
+        <v>129671717</v>
       </c>
       <c r="B21" t="n">
-        <v>98768</v>
+        <v>91588</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2785,10 +2784,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>781774</v>
+        <v>781823</v>
       </c>
       <c r="R21" t="n">
-        <v>7143251</v>
+        <v>7143286</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2821,11 +2820,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>3 x 1 meter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2856,7 +2850,7 @@
         <v>129671769</v>
       </c>
       <c r="B22" t="n">
-        <v>91551</v>
+        <v>91552</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2958,41 +2952,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129671437</v>
+        <v>129671688</v>
       </c>
       <c r="B23" t="n">
-        <v>82910</v>
+        <v>98769</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3000,10 +2995,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>781567</v>
+        <v>781774</v>
       </c>
       <c r="R23" t="n">
-        <v>7143316</v>
+        <v>7143251</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3030,17 +3025,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>på krokig gammelgran</t>
+          <t>3 x 1 meter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3068,10 +3063,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129671717</v>
+        <v>129671522</v>
       </c>
       <c r="B24" t="n">
-        <v>91587</v>
+        <v>57733</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3079,30 +3074,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3110,10 +3106,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>781823</v>
+        <v>781374</v>
       </c>
       <c r="R24" t="n">
-        <v>7143286</v>
+        <v>7143326</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3140,12 +3136,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>färska hål i gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3154,7 +3155,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3173,41 +3173,42 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129671363</v>
+        <v>129671328</v>
       </c>
       <c r="B25" t="n">
-        <v>79075</v>
+        <v>98769</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3215,10 +3216,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>781284</v>
+        <v>781377</v>
       </c>
       <c r="R25" t="n">
-        <v>7143261</v>
+        <v>7143460</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3251,6 +3252,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>ca 1 x 1 meter med bladrosetter</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3278,10 +3284,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129671328</v>
+        <v>129671422</v>
       </c>
       <c r="B26" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3321,10 +3327,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>781377</v>
+        <v>781559</v>
       </c>
       <c r="R26" t="n">
-        <v>7143460</v>
+        <v>7143298</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3361,7 +3367,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>ca 1 x 1 meter med bladrosetter</t>
+          <t>ca 2 x 2 meter med bladrosetter</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3389,42 +3395,41 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129671422</v>
+        <v>129671363</v>
       </c>
       <c r="B27" t="n">
-        <v>98768</v>
+        <v>79076</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3432,10 +3437,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>781559</v>
+        <v>781284</v>
       </c>
       <c r="R27" t="n">
-        <v>7143298</v>
+        <v>7143261</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3468,11 +3473,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>ca 2 x 2 meter med bladrosetter</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3503,7 +3503,7 @@
         <v>129671572</v>
       </c>
       <c r="B28" t="n">
-        <v>91607</v>
+        <v>91608</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         <v>129671659</v>
       </c>
       <c r="B29" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         <v>129671514</v>
       </c>
       <c r="B30" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>129671632</v>
       </c>
       <c r="B31" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         <v>129671647</v>
       </c>
       <c r="B32" t="n">
-        <v>82910</v>
+        <v>82911</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>129671752</v>
       </c>
       <c r="B33" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129670180</v>
+        <v>129671452</v>
       </c>
       <c r="B34" t="n">
-        <v>91969</v>
+        <v>98769</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4145,30 +4145,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1506</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4176,10 +4177,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>781534</v>
+        <v>781558</v>
       </c>
       <c r="R34" t="n">
-        <v>7143302</v>
+        <v>7143348</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4212,11 +4213,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>på granlåga med ullticka, kötticka och rosenticka</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4244,42 +4240,41 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129671316</v>
+        <v>129670180</v>
       </c>
       <c r="B35" t="n">
-        <v>57732</v>
+        <v>91970</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>1506</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4287,10 +4282,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>781538</v>
+        <v>781534</v>
       </c>
       <c r="R35" t="n">
-        <v>7143358</v>
+        <v>7143302</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4327,7 +4322,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>hål i högstubbe</t>
+          <t>på granlåga med ullticka, kötticka och rosenticka</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4336,6 +4331,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4354,42 +4350,42 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129671452</v>
+        <v>129671316</v>
       </c>
       <c r="B36" t="n">
-        <v>98768</v>
+        <v>57733</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4397,10 +4393,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>781558</v>
+        <v>781538</v>
       </c>
       <c r="R36" t="n">
-        <v>7143348</v>
+        <v>7143358</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4435,13 +4431,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>hål i högstubbe</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 48749-2025 artfynd.xlsx
+++ b/artfynd/A 48749-2025 artfynd.xlsx
@@ -1548,42 +1548,41 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129671431</v>
+        <v>129671725</v>
       </c>
       <c r="B10" t="n">
-        <v>98769</v>
+        <v>91588</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1591,10 +1590,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>781554</v>
+        <v>781721</v>
       </c>
       <c r="R10" t="n">
-        <v>7143299</v>
+        <v>7143412</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1621,12 +1620,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1654,7 +1653,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129671399</v>
+        <v>129671431</v>
       </c>
       <c r="B11" t="n">
         <v>98769</v>
@@ -1688,11 +1687,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1701,10 +1696,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>781522</v>
+        <v>781554</v>
       </c>
       <c r="R11" t="n">
-        <v>7143269</v>
+        <v>7143299</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1737,11 +1732,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>med överblommad blomstängel</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1769,41 +1759,46 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129671725</v>
+        <v>129671399</v>
       </c>
       <c r="B12" t="n">
-        <v>91588</v>
+        <v>98769</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1811,10 +1806,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>781721</v>
+        <v>781522</v>
       </c>
       <c r="R12" t="n">
-        <v>7143412</v>
+        <v>7143269</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,12 +1836,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>med överblommad blomstängel</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2417,10 +2417,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129671643</v>
+        <v>129671583</v>
       </c>
       <c r="B18" t="n">
-        <v>91539</v>
+        <v>57733</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2428,30 +2428,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>112</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2459,10 +2460,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>781633</v>
+        <v>781512</v>
       </c>
       <c r="R18" t="n">
-        <v>7143286</v>
+        <v>7143186</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2497,13 +2498,17 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>färskt hål i tall</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2522,10 +2527,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129671583</v>
+        <v>129671643</v>
       </c>
       <c r="B19" t="n">
-        <v>57733</v>
+        <v>91539</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2533,31 +2538,30 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>112</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2565,10 +2569,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>781512</v>
+        <v>781633</v>
       </c>
       <c r="R19" t="n">
-        <v>7143186</v>
+        <v>7143286</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2603,17 +2607,13 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>färskt hål i tall</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2847,41 +2847,42 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129671769</v>
+        <v>129671522</v>
       </c>
       <c r="B22" t="n">
-        <v>91552</v>
+        <v>57733</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2889,10 +2890,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>781492</v>
+        <v>781374</v>
       </c>
       <c r="R22" t="n">
-        <v>7143441</v>
+        <v>7143326</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2919,12 +2920,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>färska hål i gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2933,7 +2939,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2952,42 +2957,41 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129671688</v>
+        <v>129671769</v>
       </c>
       <c r="B23" t="n">
-        <v>98769</v>
+        <v>91552</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2995,10 +2999,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>781774</v>
+        <v>781492</v>
       </c>
       <c r="R23" t="n">
-        <v>7143251</v>
+        <v>7143441</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3031,11 +3035,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>3 x 1 meter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3063,42 +3062,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129671522</v>
+        <v>129671688</v>
       </c>
       <c r="B24" t="n">
-        <v>57733</v>
+        <v>98769</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3106,10 +3105,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>781374</v>
+        <v>781774</v>
       </c>
       <c r="R24" t="n">
-        <v>7143326</v>
+        <v>7143251</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3136,17 +3135,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>färska hål i gran</t>
+          <t>3 x 1 meter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3155,6 +3154,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 48749-2025 artfynd.xlsx
+++ b/artfynd/A 48749-2025 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>129671679</v>
       </c>
       <c r="B3" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>129671353</v>
       </c>
       <c r="B4" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,42 +997,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129671604</v>
+        <v>129671369</v>
       </c>
       <c r="B5" t="n">
-        <v>57733</v>
+        <v>98774</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>781583</v>
+        <v>781313</v>
       </c>
       <c r="R5" t="n">
-        <v>7143145</v>
+        <v>7143250</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1070,17 +1070,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>hack i låga</t>
+          <t>ca 1 x 3 meter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1089,6 +1089,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1107,42 +1108,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129671369</v>
+        <v>129671604</v>
       </c>
       <c r="B6" t="n">
-        <v>98769</v>
+        <v>57733</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1150,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>781313</v>
+        <v>781583</v>
       </c>
       <c r="R6" t="n">
-        <v>7143250</v>
+        <v>7143145</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,17 +1181,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ca 1 x 3 meter med bladrosetter!</t>
+          <t>hack i låga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1199,7 +1200,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1441,7 +1441,7 @@
         <v>129670173</v>
       </c>
       <c r="B9" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,41 +1548,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129671725</v>
+        <v>129671431</v>
       </c>
       <c r="B10" t="n">
-        <v>91588</v>
+        <v>98774</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1590,10 +1591,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>781721</v>
+        <v>781554</v>
       </c>
       <c r="R10" t="n">
-        <v>7143412</v>
+        <v>7143299</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1620,12 +1621,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,10 +1654,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129671431</v>
+        <v>129671399</v>
       </c>
       <c r="B11" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1687,7 +1688,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1696,10 +1701,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>781554</v>
+        <v>781522</v>
       </c>
       <c r="R11" t="n">
-        <v>7143299</v>
+        <v>7143269</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1732,6 +1737,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>med överblommad blomstängel</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1759,46 +1769,41 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129671399</v>
+        <v>129671725</v>
       </c>
       <c r="B12" t="n">
-        <v>98769</v>
+        <v>91593</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1806,10 +1811,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>781522</v>
+        <v>781721</v>
       </c>
       <c r="R12" t="n">
-        <v>7143269</v>
+        <v>7143412</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1836,17 +1841,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>med överblommad blomstängel</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1877,7 +1877,7 @@
         <v>129670229</v>
       </c>
       <c r="B13" t="n">
-        <v>91886</v>
+        <v>91891</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1984,10 +1984,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129670096</v>
+        <v>129671776</v>
       </c>
       <c r="B14" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2013,11 +2013,7 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -2027,10 +2023,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>781314</v>
+        <v>781537</v>
       </c>
       <c r="R14" t="n">
-        <v>7143242</v>
+        <v>7143351</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2057,17 +2053,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ca 1x1 meter med bladrosetter</t>
+          <t>ca 2 x 1 m med bladrosetter</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2095,42 +2091,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129670107</v>
+        <v>129670096</v>
       </c>
       <c r="B15" t="n">
-        <v>57733</v>
+        <v>98774</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2138,10 +2134,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>781364</v>
+        <v>781314</v>
       </c>
       <c r="R15" t="n">
-        <v>7143210</v>
+        <v>7143242</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2178,7 +2174,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>hål i naturlig granstubbe</t>
+          <t>ca 1x1 meter med bladrosetter</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2187,6 +2183,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2205,38 +2202,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129671776</v>
+        <v>129670107</v>
       </c>
       <c r="B16" t="n">
-        <v>98769</v>
+        <v>57733</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2244,10 +2245,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>781537</v>
+        <v>781364</v>
       </c>
       <c r="R16" t="n">
-        <v>7143351</v>
+        <v>7143210</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2274,17 +2275,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ca 2 x 1 m med bladrosetter</t>
+          <t>hål i naturlig granstubbe</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2293,7 +2294,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2315,7 +2315,7 @@
         <v>129671733</v>
       </c>
       <c r="B17" t="n">
-        <v>82911</v>
+        <v>82916</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2417,10 +2417,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129671583</v>
+        <v>129671643</v>
       </c>
       <c r="B18" t="n">
-        <v>57733</v>
+        <v>91544</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2428,31 +2428,30 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>112</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2460,10 +2459,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>781512</v>
+        <v>781633</v>
       </c>
       <c r="R18" t="n">
-        <v>7143186</v>
+        <v>7143286</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2498,17 +2497,13 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>färskt hål i tall</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2527,10 +2522,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129671643</v>
+        <v>129671583</v>
       </c>
       <c r="B19" t="n">
-        <v>91539</v>
+        <v>57733</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2538,30 +2533,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>112</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2569,10 +2565,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>781633</v>
+        <v>781512</v>
       </c>
       <c r="R19" t="n">
-        <v>7143286</v>
+        <v>7143186</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2607,13 +2603,17 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>färskt hål i tall</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2635,7 +2635,7 @@
         <v>129671437</v>
       </c>
       <c r="B20" t="n">
-        <v>82911</v>
+        <v>82916</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2745,7 +2745,7 @@
         <v>129671717</v>
       </c>
       <c r="B21" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2847,42 +2847,41 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129671522</v>
+        <v>129671769</v>
       </c>
       <c r="B22" t="n">
-        <v>57733</v>
+        <v>91557</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2890,10 +2889,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>781374</v>
+        <v>781492</v>
       </c>
       <c r="R22" t="n">
-        <v>7143326</v>
+        <v>7143441</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2920,17 +2919,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>färska hål i gran</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2939,6 +2933,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2957,41 +2952,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129671769</v>
+        <v>129671522</v>
       </c>
       <c r="B23" t="n">
-        <v>91552</v>
+        <v>57733</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2999,10 +2995,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>781492</v>
+        <v>781374</v>
       </c>
       <c r="R23" t="n">
-        <v>7143441</v>
+        <v>7143326</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3029,12 +3025,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>färska hål i gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3043,7 +3044,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3065,7 +3065,7 @@
         <v>129671688</v>
       </c>
       <c r="B24" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>129671328</v>
       </c>
       <c r="B25" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         <v>129671422</v>
       </c>
       <c r="B26" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         <v>129671363</v>
       </c>
       <c r="B27" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>129671572</v>
       </c>
       <c r="B28" t="n">
-        <v>91608</v>
+        <v>91613</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         <v>129671659</v>
       </c>
       <c r="B29" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3707,10 +3707,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129671514</v>
+        <v>129671632</v>
       </c>
       <c r="B30" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3718,16 +3718,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3738,11 +3738,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3750,10 +3746,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>781563</v>
+        <v>781623</v>
       </c>
       <c r="R30" t="n">
-        <v>7143446</v>
+        <v>7143270</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3780,17 +3776,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>färska hål</t>
+          <t>gammalt bohål i granlåga, rätt storlek för tretåig hackspett</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3817,10 +3813,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129671632</v>
+        <v>129671514</v>
       </c>
       <c r="B31" t="n">
-        <v>57736</v>
+        <v>57733</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3828,16 +3824,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3848,7 +3844,11 @@
       <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3856,10 +3856,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>781623</v>
+        <v>781563</v>
       </c>
       <c r="R31" t="n">
-        <v>7143270</v>
+        <v>7143446</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3886,17 +3886,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>gammalt bohål i granlåga, rätt storlek för tretåig hackspett</t>
+          <t>färska hål</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3926,7 +3926,7 @@
         <v>129671647</v>
       </c>
       <c r="B32" t="n">
-        <v>82911</v>
+        <v>82916</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>129671752</v>
       </c>
       <c r="B33" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4134,42 +4134,42 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129671452</v>
+        <v>129671316</v>
       </c>
       <c r="B34" t="n">
-        <v>98769</v>
+        <v>57733</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4177,10 +4177,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>781558</v>
+        <v>781538</v>
       </c>
       <c r="R34" t="n">
-        <v>7143348</v>
+        <v>7143358</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4215,13 +4215,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>hål i högstubbe</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4243,7 +4247,7 @@
         <v>129670180</v>
       </c>
       <c r="B35" t="n">
-        <v>91970</v>
+        <v>91975</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4350,42 +4354,42 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129671316</v>
+        <v>129671452</v>
       </c>
       <c r="B36" t="n">
-        <v>57733</v>
+        <v>98774</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4393,10 +4397,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>781538</v>
+        <v>781558</v>
       </c>
       <c r="R36" t="n">
-        <v>7143358</v>
+        <v>7143348</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4431,17 +4435,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>hål i högstubbe</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 48749-2025 artfynd.xlsx
+++ b/artfynd/A 48749-2025 artfynd.xlsx
@@ -997,42 +997,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129671369</v>
+        <v>129671604</v>
       </c>
       <c r="B5" t="n">
-        <v>98774</v>
+        <v>57733</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>781313</v>
+        <v>781583</v>
       </c>
       <c r="R5" t="n">
-        <v>7143250</v>
+        <v>7143145</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1070,17 +1070,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ca 1 x 3 meter med bladrosetter!</t>
+          <t>hack i låga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1089,7 +1089,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1108,42 +1107,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129671604</v>
+        <v>129671369</v>
       </c>
       <c r="B6" t="n">
-        <v>57733</v>
+        <v>98774</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1151,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>781583</v>
+        <v>781313</v>
       </c>
       <c r="R6" t="n">
-        <v>7143145</v>
+        <v>7143250</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,17 +1180,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>hack i låga</t>
+          <t>ca 1 x 3 meter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,6 +1199,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1548,42 +1548,41 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129671431</v>
+        <v>129671725</v>
       </c>
       <c r="B10" t="n">
-        <v>98774</v>
+        <v>91593</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1591,10 +1590,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>781554</v>
+        <v>781721</v>
       </c>
       <c r="R10" t="n">
-        <v>7143299</v>
+        <v>7143412</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1621,12 +1620,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1654,7 +1653,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129671399</v>
+        <v>129671431</v>
       </c>
       <c r="B11" t="n">
         <v>98774</v>
@@ -1688,11 +1687,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1701,10 +1696,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>781522</v>
+        <v>781554</v>
       </c>
       <c r="R11" t="n">
-        <v>7143269</v>
+        <v>7143299</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1737,11 +1732,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>med överblommad blomstängel</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1769,41 +1759,46 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129671725</v>
+        <v>129671399</v>
       </c>
       <c r="B12" t="n">
-        <v>91593</v>
+        <v>98774</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1811,10 +1806,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>781721</v>
+        <v>781522</v>
       </c>
       <c r="R12" t="n">
-        <v>7143412</v>
+        <v>7143269</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,12 +1836,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>med överblommad blomstängel</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1874,41 +1874,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129670229</v>
+        <v>129671776</v>
       </c>
       <c r="B13" t="n">
-        <v>91891</v>
+        <v>98774</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1916,10 +1913,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>781534</v>
+        <v>781537</v>
       </c>
       <c r="R13" t="n">
-        <v>7143302</v>
+        <v>7143351</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1946,17 +1943,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>på samma låga som ostticka, kötticka och ullticka</t>
+          <t>ca 2 x 1 m med bladrosetter</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1984,7 +1981,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129671776</v>
+        <v>129670096</v>
       </c>
       <c r="B14" t="n">
         <v>98774</v>
@@ -2013,7 +2010,11 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -2023,10 +2024,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>781537</v>
+        <v>781314</v>
       </c>
       <c r="R14" t="n">
-        <v>7143351</v>
+        <v>7143242</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,17 +2054,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ca 2 x 1 m med bladrosetter</t>
+          <t>ca 1x1 meter med bladrosetter</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2091,42 +2092,41 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129670096</v>
+        <v>129670229</v>
       </c>
       <c r="B15" t="n">
-        <v>98774</v>
+        <v>91891</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2134,10 +2134,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>781314</v>
+        <v>781534</v>
       </c>
       <c r="R15" t="n">
-        <v>7143242</v>
+        <v>7143302</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ca 1x1 meter med bladrosetter</t>
+          <t>på samma låga som ostticka, kötticka och ullticka</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2417,10 +2417,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129671643</v>
+        <v>129671583</v>
       </c>
       <c r="B18" t="n">
-        <v>91544</v>
+        <v>57733</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2428,30 +2428,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>112</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2459,10 +2460,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>781633</v>
+        <v>781512</v>
       </c>
       <c r="R18" t="n">
-        <v>7143286</v>
+        <v>7143186</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2497,13 +2498,17 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>färskt hål i tall</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2522,10 +2527,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129671583</v>
+        <v>129671643</v>
       </c>
       <c r="B19" t="n">
-        <v>57733</v>
+        <v>91544</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2533,31 +2538,30 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>112</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2565,10 +2569,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>781512</v>
+        <v>781633</v>
       </c>
       <c r="R19" t="n">
-        <v>7143186</v>
+        <v>7143286</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2603,17 +2607,13 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>färskt hål i tall</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129671437</v>
+        <v>129671522</v>
       </c>
       <c r="B20" t="n">
-        <v>82916</v>
+        <v>57733</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2643,30 +2643,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2674,10 +2675,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>781567</v>
+        <v>781374</v>
       </c>
       <c r="R20" t="n">
-        <v>7143316</v>
+        <v>7143326</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2714,7 +2715,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>på krokig gammelgran</t>
+          <t>färska hål i gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2723,7 +2724,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2742,32 +2742,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129671717</v>
+        <v>129671769</v>
       </c>
       <c r="B21" t="n">
-        <v>91593</v>
+        <v>91557</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2784,10 +2784,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>781823</v>
+        <v>781492</v>
       </c>
       <c r="R21" t="n">
-        <v>7143286</v>
+        <v>7143441</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2847,32 +2847,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129671769</v>
+        <v>129671437</v>
       </c>
       <c r="B22" t="n">
-        <v>91557</v>
+        <v>82916</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>781492</v>
+        <v>781567</v>
       </c>
       <c r="R22" t="n">
-        <v>7143441</v>
+        <v>7143316</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2919,12 +2919,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>på krokig gammelgran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2952,10 +2957,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129671522</v>
+        <v>129671717</v>
       </c>
       <c r="B23" t="n">
-        <v>57733</v>
+        <v>91593</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2963,31 +2968,30 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2995,10 +2999,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>781374</v>
+        <v>781823</v>
       </c>
       <c r="R23" t="n">
-        <v>7143326</v>
+        <v>7143286</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3025,17 +3029,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>färska hål i gran</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3044,6 +3043,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3707,10 +3707,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129671632</v>
+        <v>129671514</v>
       </c>
       <c r="B30" t="n">
-        <v>57736</v>
+        <v>57733</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3718,16 +3718,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3738,7 +3738,11 @@
       <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3746,10 +3750,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>781623</v>
+        <v>781563</v>
       </c>
       <c r="R30" t="n">
-        <v>7143270</v>
+        <v>7143446</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3776,17 +3780,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>gammalt bohål i granlåga, rätt storlek för tretåig hackspett</t>
+          <t>färska hål</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3813,10 +3817,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129671514</v>
+        <v>129671632</v>
       </c>
       <c r="B31" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3824,16 +3828,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3844,11 +3848,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3856,10 +3856,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>781563</v>
+        <v>781623</v>
       </c>
       <c r="R31" t="n">
-        <v>7143446</v>
+        <v>7143270</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3886,17 +3886,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>färska hål</t>
+          <t>gammalt bohål i granlåga, rätt storlek för tretåig hackspett</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4134,42 +4134,41 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129671316</v>
+        <v>129670180</v>
       </c>
       <c r="B34" t="n">
-        <v>57733</v>
+        <v>91975</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>1506</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4177,10 +4176,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>781538</v>
+        <v>781534</v>
       </c>
       <c r="R34" t="n">
-        <v>7143358</v>
+        <v>7143302</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4217,7 +4216,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>hål i högstubbe</t>
+          <t>på granlåga med ullticka, kötticka och rosenticka</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4226,6 +4225,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4244,41 +4244,42 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129670180</v>
+        <v>129671316</v>
       </c>
       <c r="B35" t="n">
-        <v>91975</v>
+        <v>57733</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1506</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4286,10 +4287,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>781534</v>
+        <v>781538</v>
       </c>
       <c r="R35" t="n">
-        <v>7143302</v>
+        <v>7143358</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4326,7 +4327,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>på granlåga med ullticka, kötticka och rosenticka</t>
+          <t>hål i högstubbe</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4335,7 +4336,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 48749-2025 artfynd.xlsx
+++ b/artfynd/A 48749-2025 artfynd.xlsx
@@ -1874,38 +1874,41 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129671776</v>
+        <v>129670229</v>
       </c>
       <c r="B13" t="n">
-        <v>98774</v>
+        <v>91891</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1913,10 +1916,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>781537</v>
+        <v>781534</v>
       </c>
       <c r="R13" t="n">
-        <v>7143351</v>
+        <v>7143302</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1943,17 +1946,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ca 2 x 1 m med bladrosetter</t>
+          <t>på samma låga som ostticka, kötticka och ullticka</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1981,42 +1984,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129670096</v>
+        <v>129670107</v>
       </c>
       <c r="B14" t="n">
-        <v>98774</v>
+        <v>57733</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2024,10 +2027,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>781314</v>
+        <v>781364</v>
       </c>
       <c r="R14" t="n">
-        <v>7143242</v>
+        <v>7143210</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2064,7 +2067,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ca 1x1 meter med bladrosetter</t>
+          <t>hål i naturlig granstubbe</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2073,7 +2076,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2092,41 +2094,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129670229</v>
+        <v>129671776</v>
       </c>
       <c r="B15" t="n">
-        <v>91891</v>
+        <v>98774</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2134,10 +2133,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>781534</v>
+        <v>781537</v>
       </c>
       <c r="R15" t="n">
-        <v>7143302</v>
+        <v>7143351</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2164,17 +2163,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>på samma låga som ostticka, kötticka och ullticka</t>
+          <t>ca 2 x 1 m med bladrosetter</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2202,42 +2201,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129670107</v>
+        <v>129670096</v>
       </c>
       <c r="B16" t="n">
-        <v>57733</v>
+        <v>98774</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2245,10 +2244,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>781364</v>
+        <v>781314</v>
       </c>
       <c r="R16" t="n">
-        <v>7143210</v>
+        <v>7143242</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2285,7 +2284,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>hål i naturlig granstubbe</t>
+          <t>ca 1x1 meter med bladrosetter</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2294,6 +2293,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2417,10 +2417,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129671583</v>
+        <v>129671643</v>
       </c>
       <c r="B18" t="n">
-        <v>57733</v>
+        <v>91544</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2428,31 +2428,30 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>112</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2460,10 +2459,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>781512</v>
+        <v>781633</v>
       </c>
       <c r="R18" t="n">
-        <v>7143186</v>
+        <v>7143286</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2498,17 +2497,13 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>färskt hål i tall</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2527,10 +2522,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129671643</v>
+        <v>129671583</v>
       </c>
       <c r="B19" t="n">
-        <v>91544</v>
+        <v>57733</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2538,30 +2533,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>112</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2569,10 +2565,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>781633</v>
+        <v>781512</v>
       </c>
       <c r="R19" t="n">
-        <v>7143286</v>
+        <v>7143186</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2607,13 +2603,17 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>färskt hål i tall</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129671522</v>
+        <v>129671437</v>
       </c>
       <c r="B20" t="n">
-        <v>57733</v>
+        <v>82916</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2643,31 +2643,30 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2675,10 +2674,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>781374</v>
+        <v>781567</v>
       </c>
       <c r="R20" t="n">
-        <v>7143326</v>
+        <v>7143316</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2715,7 +2714,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>färska hål i gran</t>
+          <t>på krokig gammelgran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2724,6 +2723,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2742,32 +2742,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129671769</v>
+        <v>129671717</v>
       </c>
       <c r="B21" t="n">
-        <v>91557</v>
+        <v>91593</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2784,10 +2784,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>781492</v>
+        <v>781823</v>
       </c>
       <c r="R21" t="n">
-        <v>7143441</v>
+        <v>7143286</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2847,32 +2847,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129671437</v>
+        <v>129671769</v>
       </c>
       <c r="B22" t="n">
-        <v>82916</v>
+        <v>91557</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>781567</v>
+        <v>781492</v>
       </c>
       <c r="R22" t="n">
-        <v>7143316</v>
+        <v>7143441</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2919,17 +2919,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>på krokig gammelgran</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2957,10 +2952,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129671717</v>
+        <v>129671522</v>
       </c>
       <c r="B23" t="n">
-        <v>91593</v>
+        <v>57733</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2968,30 +2963,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2999,10 +2995,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>781823</v>
+        <v>781374</v>
       </c>
       <c r="R23" t="n">
-        <v>7143286</v>
+        <v>7143326</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3029,12 +3025,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>färska hål i gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3043,7 +3044,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3173,42 +3173,41 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129671328</v>
+        <v>129671363</v>
       </c>
       <c r="B25" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3216,10 +3215,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>781377</v>
+        <v>781284</v>
       </c>
       <c r="R25" t="n">
-        <v>7143460</v>
+        <v>7143261</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3252,11 +3251,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>ca 1 x 1 meter med bladrosetter</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3284,7 +3278,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129671422</v>
+        <v>129671328</v>
       </c>
       <c r="B26" t="n">
         <v>98774</v>
@@ -3327,10 +3321,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>781559</v>
+        <v>781377</v>
       </c>
       <c r="R26" t="n">
-        <v>7143298</v>
+        <v>7143460</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3367,7 +3361,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>ca 2 x 2 meter med bladrosetter</t>
+          <t>ca 1 x 1 meter med bladrosetter</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3395,41 +3389,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129671363</v>
+        <v>129671422</v>
       </c>
       <c r="B27" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3437,10 +3432,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>781284</v>
+        <v>781559</v>
       </c>
       <c r="R27" t="n">
-        <v>7143261</v>
+        <v>7143298</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3473,6 +3468,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>ca 2 x 2 meter med bladrosetter</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 48749-2025 artfynd.xlsx
+++ b/artfynd/A 48749-2025 artfynd.xlsx
@@ -997,42 +997,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129671604</v>
+        <v>129671369</v>
       </c>
       <c r="B5" t="n">
-        <v>57733</v>
+        <v>98774</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>781583</v>
+        <v>781313</v>
       </c>
       <c r="R5" t="n">
-        <v>7143145</v>
+        <v>7143250</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1070,17 +1070,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>hack i låga</t>
+          <t>ca 1 x 3 meter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1089,6 +1089,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1107,42 +1108,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129671369</v>
+        <v>129671604</v>
       </c>
       <c r="B6" t="n">
-        <v>98774</v>
+        <v>57733</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1150,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>781313</v>
+        <v>781583</v>
       </c>
       <c r="R6" t="n">
-        <v>7143250</v>
+        <v>7143145</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,17 +1181,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ca 1 x 3 meter med bladrosetter!</t>
+          <t>hack i låga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1199,7 +1200,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1874,41 +1874,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129670229</v>
+        <v>129671776</v>
       </c>
       <c r="B13" t="n">
-        <v>91891</v>
+        <v>98774</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1916,10 +1913,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>781534</v>
+        <v>781537</v>
       </c>
       <c r="R13" t="n">
-        <v>7143302</v>
+        <v>7143351</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1946,17 +1943,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>på samma låga som ostticka, kötticka och ullticka</t>
+          <t>ca 2 x 1 m med bladrosetter</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1984,42 +1981,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129670107</v>
+        <v>129670096</v>
       </c>
       <c r="B14" t="n">
-        <v>57733</v>
+        <v>98774</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2027,10 +2024,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>781364</v>
+        <v>781314</v>
       </c>
       <c r="R14" t="n">
-        <v>7143210</v>
+        <v>7143242</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2067,7 +2064,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>hål i naturlig granstubbe</t>
+          <t>ca 1x1 meter med bladrosetter</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2076,6 +2073,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2094,38 +2092,41 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129671776</v>
+        <v>129670229</v>
       </c>
       <c r="B15" t="n">
-        <v>98774</v>
+        <v>91891</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2133,10 +2134,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>781537</v>
+        <v>781534</v>
       </c>
       <c r="R15" t="n">
-        <v>7143351</v>
+        <v>7143302</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2163,17 +2164,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ca 2 x 1 m med bladrosetter</t>
+          <t>på samma låga som ostticka, kötticka och ullticka</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2201,42 +2202,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129670096</v>
+        <v>129670107</v>
       </c>
       <c r="B16" t="n">
-        <v>98774</v>
+        <v>57733</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2244,10 +2245,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>781314</v>
+        <v>781364</v>
       </c>
       <c r="R16" t="n">
-        <v>7143242</v>
+        <v>7143210</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2284,7 +2285,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ca 1x1 meter med bladrosetter</t>
+          <t>hål i naturlig granstubbe</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2293,7 +2294,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2952,42 +2952,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129671522</v>
+        <v>129671688</v>
       </c>
       <c r="B23" t="n">
-        <v>57733</v>
+        <v>98774</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2995,10 +2995,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>781374</v>
+        <v>781774</v>
       </c>
       <c r="R23" t="n">
-        <v>7143326</v>
+        <v>7143251</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3025,17 +3025,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>färska hål i gran</t>
+          <t>3 x 1 meter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3044,6 +3044,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3062,42 +3063,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129671688</v>
+        <v>129671522</v>
       </c>
       <c r="B24" t="n">
-        <v>98774</v>
+        <v>57733</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3105,10 +3106,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>781774</v>
+        <v>781374</v>
       </c>
       <c r="R24" t="n">
-        <v>7143251</v>
+        <v>7143326</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3135,17 +3136,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>3 x 1 meter med bladrosetter!</t>
+          <t>färska hål i gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3154,7 +3155,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 48749-2025 artfynd.xlsx
+++ b/artfynd/A 48749-2025 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>129671679</v>
       </c>
       <c r="B3" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>129671353</v>
       </c>
       <c r="B4" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,42 +997,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129671369</v>
+        <v>129671604</v>
       </c>
       <c r="B5" t="n">
-        <v>98774</v>
+        <v>57733</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>781313</v>
+        <v>781583</v>
       </c>
       <c r="R5" t="n">
-        <v>7143250</v>
+        <v>7143145</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1070,17 +1070,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ca 1 x 3 meter med bladrosetter!</t>
+          <t>hack i låga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1089,7 +1089,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1108,42 +1107,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129671604</v>
+        <v>129671369</v>
       </c>
       <c r="B6" t="n">
-        <v>57733</v>
+        <v>98778</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1151,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>781583</v>
+        <v>781313</v>
       </c>
       <c r="R6" t="n">
-        <v>7143145</v>
+        <v>7143250</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,17 +1180,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>hack i låga</t>
+          <t>ca 1 x 3 meter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,6 +1199,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1441,7 +1441,7 @@
         <v>129670173</v>
       </c>
       <c r="B9" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,41 +1548,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129671725</v>
+        <v>129671431</v>
       </c>
       <c r="B10" t="n">
-        <v>91593</v>
+        <v>98778</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1590,10 +1591,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>781721</v>
+        <v>781554</v>
       </c>
       <c r="R10" t="n">
-        <v>7143412</v>
+        <v>7143299</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1620,12 +1621,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,10 +1654,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129671431</v>
+        <v>129671399</v>
       </c>
       <c r="B11" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1687,7 +1688,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1696,10 +1701,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>781554</v>
+        <v>781522</v>
       </c>
       <c r="R11" t="n">
-        <v>7143299</v>
+        <v>7143269</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1732,6 +1737,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>med överblommad blomstängel</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1759,46 +1769,41 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129671399</v>
+        <v>129671725</v>
       </c>
       <c r="B12" t="n">
-        <v>98774</v>
+        <v>91597</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1806,10 +1811,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>781522</v>
+        <v>781721</v>
       </c>
       <c r="R12" t="n">
-        <v>7143269</v>
+        <v>7143412</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1836,17 +1841,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>med överblommad blomstängel</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1874,38 +1874,41 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129671776</v>
+        <v>129670229</v>
       </c>
       <c r="B13" t="n">
-        <v>98774</v>
+        <v>91895</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1913,10 +1916,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>781537</v>
+        <v>781534</v>
       </c>
       <c r="R13" t="n">
-        <v>7143351</v>
+        <v>7143302</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1943,17 +1946,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ca 2 x 1 m med bladrosetter</t>
+          <t>på samma låga som ostticka, kötticka och ullticka</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1981,42 +1984,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129670096</v>
+        <v>129670107</v>
       </c>
       <c r="B14" t="n">
-        <v>98774</v>
+        <v>57733</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2024,10 +2027,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>781314</v>
+        <v>781364</v>
       </c>
       <c r="R14" t="n">
-        <v>7143242</v>
+        <v>7143210</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2064,7 +2067,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ca 1x1 meter med bladrosetter</t>
+          <t>hål i naturlig granstubbe</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2073,7 +2076,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2092,41 +2094,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129670229</v>
+        <v>129671776</v>
       </c>
       <c r="B15" t="n">
-        <v>91891</v>
+        <v>98778</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2134,10 +2133,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>781534</v>
+        <v>781537</v>
       </c>
       <c r="R15" t="n">
-        <v>7143302</v>
+        <v>7143351</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2164,17 +2163,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>på samma låga som ostticka, kötticka och ullticka</t>
+          <t>ca 2 x 1 m med bladrosetter</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2202,42 +2201,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129670107</v>
+        <v>129670096</v>
       </c>
       <c r="B16" t="n">
-        <v>57733</v>
+        <v>98778</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2245,10 +2244,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>781364</v>
+        <v>781314</v>
       </c>
       <c r="R16" t="n">
-        <v>7143210</v>
+        <v>7143242</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2285,7 +2284,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>hål i naturlig granstubbe</t>
+          <t>ca 1x1 meter med bladrosetter</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2294,6 +2293,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2420,7 +2420,7 @@
         <v>129671643</v>
       </c>
       <c r="B18" t="n">
-        <v>91544</v>
+        <v>91548</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2632,32 +2632,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129671437</v>
+        <v>129671769</v>
       </c>
       <c r="B20" t="n">
-        <v>82916</v>
+        <v>91561</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2674,10 +2674,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>781567</v>
+        <v>781492</v>
       </c>
       <c r="R20" t="n">
-        <v>7143316</v>
+        <v>7143441</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2704,17 +2704,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>på krokig gammelgran</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2742,41 +2737,42 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129671717</v>
+        <v>129671688</v>
       </c>
       <c r="B21" t="n">
-        <v>91593</v>
+        <v>98778</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2784,10 +2780,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>781823</v>
+        <v>781774</v>
       </c>
       <c r="R21" t="n">
-        <v>7143286</v>
+        <v>7143251</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2820,6 +2816,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>3 x 1 meter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2847,32 +2848,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129671769</v>
+        <v>129671437</v>
       </c>
       <c r="B22" t="n">
-        <v>91557</v>
+        <v>82916</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2889,10 +2890,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>781492</v>
+        <v>781567</v>
       </c>
       <c r="R22" t="n">
-        <v>7143441</v>
+        <v>7143316</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2919,12 +2920,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>på krokig gammelgran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2952,42 +2958,41 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129671688</v>
+        <v>129671717</v>
       </c>
       <c r="B23" t="n">
-        <v>98774</v>
+        <v>91597</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2995,10 +3000,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>781774</v>
+        <v>781823</v>
       </c>
       <c r="R23" t="n">
-        <v>7143251</v>
+        <v>7143286</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3031,11 +3036,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>3 x 1 meter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3173,41 +3173,42 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129671363</v>
+        <v>129671328</v>
       </c>
       <c r="B25" t="n">
-        <v>79081</v>
+        <v>98778</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3215,10 +3216,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>781284</v>
+        <v>781377</v>
       </c>
       <c r="R25" t="n">
-        <v>7143261</v>
+        <v>7143460</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3251,6 +3252,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>ca 1 x 1 meter med bladrosetter</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3278,10 +3284,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129671328</v>
+        <v>129671422</v>
       </c>
       <c r="B26" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3321,10 +3327,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>781377</v>
+        <v>781559</v>
       </c>
       <c r="R26" t="n">
-        <v>7143460</v>
+        <v>7143298</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3361,7 +3367,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>ca 1 x 1 meter med bladrosetter</t>
+          <t>ca 2 x 2 meter med bladrosetter</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3389,42 +3395,41 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129671422</v>
+        <v>129671363</v>
       </c>
       <c r="B27" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3432,10 +3437,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>781559</v>
+        <v>781284</v>
       </c>
       <c r="R27" t="n">
-        <v>7143298</v>
+        <v>7143261</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3468,11 +3473,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>ca 2 x 2 meter med bladrosetter</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3503,7 +3503,7 @@
         <v>129671572</v>
       </c>
       <c r="B28" t="n">
-        <v>91613</v>
+        <v>91617</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         <v>129671659</v>
       </c>
       <c r="B29" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>129671752</v>
       </c>
       <c r="B33" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129670180</v>
+        <v>129671452</v>
       </c>
       <c r="B34" t="n">
-        <v>91975</v>
+        <v>98778</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4145,30 +4145,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1506</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4176,10 +4177,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>781534</v>
+        <v>781558</v>
       </c>
       <c r="R34" t="n">
-        <v>7143302</v>
+        <v>7143348</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4212,11 +4213,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>på granlåga med ullticka, kötticka och rosenticka</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4244,42 +4240,41 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129671316</v>
+        <v>129670180</v>
       </c>
       <c r="B35" t="n">
-        <v>57733</v>
+        <v>91979</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>1506</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4287,10 +4282,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>781538</v>
+        <v>781534</v>
       </c>
       <c r="R35" t="n">
-        <v>7143358</v>
+        <v>7143302</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4327,7 +4322,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>hål i högstubbe</t>
+          <t>på granlåga med ullticka, kötticka och rosenticka</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4336,6 +4331,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4354,42 +4350,42 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129671452</v>
+        <v>129671316</v>
       </c>
       <c r="B36" t="n">
-        <v>98774</v>
+        <v>57733</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4397,10 +4393,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>781558</v>
+        <v>781538</v>
       </c>
       <c r="R36" t="n">
-        <v>7143348</v>
+        <v>7143358</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4435,13 +4431,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>hål i högstubbe</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 48749-2025 artfynd.xlsx
+++ b/artfynd/A 48749-2025 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>129671679</v>
       </c>
       <c r="B3" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>129671353</v>
       </c>
       <c r="B4" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>129671369</v>
       </c>
       <c r="B6" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>129670173</v>
       </c>
       <c r="B9" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129671431</v>
+        <v>129671399</v>
       </c>
       <c r="B10" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,7 +1582,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1591,10 +1595,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>781554</v>
+        <v>781522</v>
       </c>
       <c r="R10" t="n">
-        <v>7143299</v>
+        <v>7143269</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1627,6 +1631,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>med överblommad blomstängel</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1654,10 +1663,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129671399</v>
+        <v>129671431</v>
       </c>
       <c r="B11" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,11 +1697,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1701,10 +1706,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>781522</v>
+        <v>781554</v>
       </c>
       <c r="R11" t="n">
-        <v>7143269</v>
+        <v>7143299</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1737,11 +1742,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>med överblommad blomstängel</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1772,7 +1772,7 @@
         <v>129671725</v>
       </c>
       <c r="B12" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1874,41 +1874,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129670229</v>
+        <v>129671776</v>
       </c>
       <c r="B13" t="n">
-        <v>91895</v>
+        <v>98780</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1916,10 +1913,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>781534</v>
+        <v>781537</v>
       </c>
       <c r="R13" t="n">
-        <v>7143302</v>
+        <v>7143351</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1946,17 +1943,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>på samma låga som ostticka, kötticka och ullticka</t>
+          <t>ca 2 x 1 m med bladrosetter</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1984,10 +1981,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129670107</v>
+        <v>129670229</v>
       </c>
       <c r="B14" t="n">
-        <v>57733</v>
+        <v>91897</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1995,31 +1992,30 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2027,10 +2023,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>781364</v>
+        <v>781534</v>
       </c>
       <c r="R14" t="n">
-        <v>7143210</v>
+        <v>7143302</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2067,7 +2063,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>hål i naturlig granstubbe</t>
+          <t>på samma låga som ostticka, kötticka och ullticka</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2076,6 +2072,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2094,38 +2091,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129671776</v>
+        <v>129670107</v>
       </c>
       <c r="B15" t="n">
-        <v>98778</v>
+        <v>57733</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2133,10 +2134,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>781537</v>
+        <v>781364</v>
       </c>
       <c r="R15" t="n">
-        <v>7143351</v>
+        <v>7143210</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2163,17 +2164,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ca 2 x 1 m med bladrosetter</t>
+          <t>hål i naturlig granstubbe</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2182,7 +2183,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2204,7 +2204,7 @@
         <v>129670096</v>
       </c>
       <c r="B16" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>129671733</v>
       </c>
       <c r="B17" t="n">
-        <v>82916</v>
+        <v>82918</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>129671643</v>
       </c>
       <c r="B18" t="n">
-        <v>91548</v>
+        <v>91550</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2632,41 +2632,42 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129671769</v>
+        <v>129671522</v>
       </c>
       <c r="B20" t="n">
-        <v>91561</v>
+        <v>57733</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2674,10 +2675,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>781492</v>
+        <v>781374</v>
       </c>
       <c r="R20" t="n">
-        <v>7143441</v>
+        <v>7143326</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2704,12 +2705,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>färska hål i gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2718,7 +2724,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2740,7 +2745,7 @@
         <v>129671688</v>
       </c>
       <c r="B21" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2848,32 +2853,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129671437</v>
+        <v>129671769</v>
       </c>
       <c r="B22" t="n">
-        <v>82916</v>
+        <v>91563</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2890,10 +2895,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>781567</v>
+        <v>781492</v>
       </c>
       <c r="R22" t="n">
-        <v>7143316</v>
+        <v>7143441</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2920,17 +2925,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>på krokig gammelgran</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2958,10 +2958,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129671717</v>
+        <v>129671437</v>
       </c>
       <c r="B23" t="n">
-        <v>91597</v>
+        <v>82918</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2969,21 +2969,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>781823</v>
+        <v>781567</v>
       </c>
       <c r="R23" t="n">
-        <v>7143286</v>
+        <v>7143316</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3030,12 +3030,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>på krokig gammelgran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3063,10 +3068,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129671522</v>
+        <v>129671717</v>
       </c>
       <c r="B24" t="n">
-        <v>57733</v>
+        <v>91599</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3074,31 +3079,30 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3106,10 +3110,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>781374</v>
+        <v>781823</v>
       </c>
       <c r="R24" t="n">
-        <v>7143326</v>
+        <v>7143286</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3136,17 +3140,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>färska hål i gran</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3155,6 +3154,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3173,10 +3173,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129671328</v>
+        <v>129671422</v>
       </c>
       <c r="B25" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3216,10 +3216,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>781377</v>
+        <v>781559</v>
       </c>
       <c r="R25" t="n">
-        <v>7143460</v>
+        <v>7143298</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3256,7 +3256,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>ca 1 x 1 meter med bladrosetter</t>
+          <t>ca 2 x 2 meter med bladrosetter</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3284,42 +3284,41 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129671422</v>
+        <v>129671363</v>
       </c>
       <c r="B26" t="n">
-        <v>98778</v>
+        <v>79081</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3327,10 +3326,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>781559</v>
+        <v>781284</v>
       </c>
       <c r="R26" t="n">
-        <v>7143298</v>
+        <v>7143261</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3363,11 +3362,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>ca 2 x 2 meter med bladrosetter</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3395,41 +3389,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129671363</v>
+        <v>129671328</v>
       </c>
       <c r="B27" t="n">
-        <v>79081</v>
+        <v>98780</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3437,10 +3432,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>781284</v>
+        <v>781377</v>
       </c>
       <c r="R27" t="n">
-        <v>7143261</v>
+        <v>7143460</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3473,6 +3468,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>ca 1 x 1 meter med bladrosetter</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3500,37 +3500,42 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129671572</v>
+        <v>129671659</v>
       </c>
       <c r="B28" t="n">
-        <v>91617</v>
+        <v>98780</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3538,10 +3543,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>781468</v>
+        <v>781711</v>
       </c>
       <c r="R28" t="n">
-        <v>7143208</v>
+        <v>7143272</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3601,42 +3606,37 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129671659</v>
+        <v>129671572</v>
       </c>
       <c r="B29" t="n">
-        <v>98778</v>
+        <v>91619</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3644,10 +3644,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>781711</v>
+        <v>781468</v>
       </c>
       <c r="R29" t="n">
-        <v>7143272</v>
+        <v>7143208</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3707,10 +3707,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129671514</v>
+        <v>129671632</v>
       </c>
       <c r="B30" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3718,16 +3718,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3738,11 +3738,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3750,10 +3746,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>781563</v>
+        <v>781623</v>
       </c>
       <c r="R30" t="n">
-        <v>7143446</v>
+        <v>7143270</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3780,17 +3776,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>färska hål</t>
+          <t>gammalt bohål i granlåga, rätt storlek för tretåig hackspett</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3817,10 +3813,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129671632</v>
+        <v>129671514</v>
       </c>
       <c r="B31" t="n">
-        <v>57736</v>
+        <v>57733</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3828,16 +3824,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3848,7 +3844,11 @@
       <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3856,10 +3856,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>781623</v>
+        <v>781563</v>
       </c>
       <c r="R31" t="n">
-        <v>7143270</v>
+        <v>7143446</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3886,17 +3886,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>gammalt bohål i granlåga, rätt storlek för tretåig hackspett</t>
+          <t>färska hål</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3926,7 +3926,7 @@
         <v>129671647</v>
       </c>
       <c r="B32" t="n">
-        <v>82916</v>
+        <v>82918</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>129671752</v>
       </c>
       <c r="B33" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4134,42 +4134,42 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129671452</v>
+        <v>129671316</v>
       </c>
       <c r="B34" t="n">
-        <v>98778</v>
+        <v>57733</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4177,10 +4177,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>781558</v>
+        <v>781538</v>
       </c>
       <c r="R34" t="n">
-        <v>7143348</v>
+        <v>7143358</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4215,13 +4215,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>hål i högstubbe</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4240,10 +4244,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129670180</v>
+        <v>129671452</v>
       </c>
       <c r="B35" t="n">
-        <v>91979</v>
+        <v>98780</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4251,30 +4255,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1506</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4282,10 +4287,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>781534</v>
+        <v>781558</v>
       </c>
       <c r="R35" t="n">
-        <v>7143302</v>
+        <v>7143348</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4318,11 +4323,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>på granlåga med ullticka, kötticka och rosenticka</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4350,42 +4350,41 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129671316</v>
+        <v>129670180</v>
       </c>
       <c r="B36" t="n">
-        <v>57733</v>
+        <v>91981</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>1506</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4393,10 +4392,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>781538</v>
+        <v>781534</v>
       </c>
       <c r="R36" t="n">
-        <v>7143358</v>
+        <v>7143302</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4433,7 +4432,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>hål i högstubbe</t>
+          <t>på granlåga med ullticka, kötticka och rosenticka</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4442,6 +4441,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 48749-2025 artfynd.xlsx
+++ b/artfynd/A 48749-2025 artfynd.xlsx
@@ -1548,46 +1548,41 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129671399</v>
+        <v>129671725</v>
       </c>
       <c r="B10" t="n">
-        <v>98780</v>
+        <v>91599</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1595,10 +1590,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>781522</v>
+        <v>781721</v>
       </c>
       <c r="R10" t="n">
-        <v>7143269</v>
+        <v>7143412</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1625,17 +1620,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>med överblommad blomstängel</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1663,7 +1653,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129671431</v>
+        <v>129671399</v>
       </c>
       <c r="B11" t="n">
         <v>98780</v>
@@ -1697,7 +1687,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1706,10 +1700,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>781554</v>
+        <v>781522</v>
       </c>
       <c r="R11" t="n">
-        <v>7143299</v>
+        <v>7143269</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1742,6 +1736,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>med överblommad blomstängel</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1769,41 +1768,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129671725</v>
+        <v>129671431</v>
       </c>
       <c r="B12" t="n">
-        <v>91599</v>
+        <v>98780</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1811,10 +1811,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>781721</v>
+        <v>781554</v>
       </c>
       <c r="R12" t="n">
-        <v>7143412</v>
+        <v>7143299</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,12 +1841,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2632,42 +2632,41 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129671522</v>
+        <v>129671769</v>
       </c>
       <c r="B20" t="n">
-        <v>57733</v>
+        <v>91563</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2675,10 +2674,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>781374</v>
+        <v>781492</v>
       </c>
       <c r="R20" t="n">
-        <v>7143326</v>
+        <v>7143441</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2705,17 +2704,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>färska hål i gran</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2724,6 +2718,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2742,42 +2737,41 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129671688</v>
+        <v>129671437</v>
       </c>
       <c r="B21" t="n">
-        <v>98780</v>
+        <v>82918</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2785,10 +2779,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>781774</v>
+        <v>781567</v>
       </c>
       <c r="R21" t="n">
-        <v>7143251</v>
+        <v>7143316</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2815,17 +2809,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>3 x 1 meter med bladrosetter!</t>
+          <t>på krokig gammelgran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2853,32 +2847,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129671769</v>
+        <v>129671717</v>
       </c>
       <c r="B22" t="n">
-        <v>91563</v>
+        <v>91599</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2895,10 +2889,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>781492</v>
+        <v>781823</v>
       </c>
       <c r="R22" t="n">
-        <v>7143441</v>
+        <v>7143286</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2958,10 +2952,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129671437</v>
+        <v>129671522</v>
       </c>
       <c r="B23" t="n">
-        <v>82918</v>
+        <v>57733</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2969,30 +2963,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3000,10 +2995,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>781567</v>
+        <v>781374</v>
       </c>
       <c r="R23" t="n">
-        <v>7143316</v>
+        <v>7143326</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3040,7 +3035,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>på krokig gammelgran</t>
+          <t>färska hål i gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3049,7 +3044,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3068,41 +3062,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129671717</v>
+        <v>129671688</v>
       </c>
       <c r="B24" t="n">
-        <v>91599</v>
+        <v>98780</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3110,10 +3105,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>781823</v>
+        <v>781774</v>
       </c>
       <c r="R24" t="n">
-        <v>7143286</v>
+        <v>7143251</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3146,6 +3141,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>3 x 1 meter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3707,10 +3707,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129671632</v>
+        <v>129671514</v>
       </c>
       <c r="B30" t="n">
-        <v>57736</v>
+        <v>57733</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3718,16 +3718,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3738,7 +3738,11 @@
       <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3746,10 +3750,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>781623</v>
+        <v>781563</v>
       </c>
       <c r="R30" t="n">
-        <v>7143270</v>
+        <v>7143446</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3776,17 +3780,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>gammalt bohål i granlåga, rätt storlek för tretåig hackspett</t>
+          <t>färska hål</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3813,10 +3817,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129671514</v>
+        <v>129671632</v>
       </c>
       <c r="B31" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3824,16 +3828,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3844,11 +3848,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3856,10 +3856,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>781563</v>
+        <v>781623</v>
       </c>
       <c r="R31" t="n">
-        <v>7143446</v>
+        <v>7143270</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3886,17 +3886,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>färska hål</t>
+          <t>gammalt bohål i granlåga, rätt storlek för tretåig hackspett</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4134,42 +4134,41 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129671316</v>
+        <v>129670180</v>
       </c>
       <c r="B34" t="n">
-        <v>57733</v>
+        <v>91981</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>1506</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4177,10 +4176,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>781538</v>
+        <v>781534</v>
       </c>
       <c r="R34" t="n">
-        <v>7143358</v>
+        <v>7143302</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4217,7 +4216,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>hål i högstubbe</t>
+          <t>på granlåga med ullticka, kötticka och rosenticka</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4226,6 +4225,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4244,42 +4244,42 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129671452</v>
+        <v>129671316</v>
       </c>
       <c r="B35" t="n">
-        <v>98780</v>
+        <v>57733</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4287,10 +4287,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>781558</v>
+        <v>781538</v>
       </c>
       <c r="R35" t="n">
-        <v>7143348</v>
+        <v>7143358</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4325,13 +4325,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>hål i högstubbe</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4350,10 +4354,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129670180</v>
+        <v>129671452</v>
       </c>
       <c r="B36" t="n">
-        <v>91981</v>
+        <v>98780</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4361,30 +4365,31 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1506</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4392,10 +4397,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>781534</v>
+        <v>781558</v>
       </c>
       <c r="R36" t="n">
-        <v>7143302</v>
+        <v>7143348</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4428,11 +4433,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>på granlåga med ullticka, kötticka och rosenticka</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 48749-2025 artfynd.xlsx
+++ b/artfynd/A 48749-2025 artfynd.xlsx
@@ -1548,41 +1548,46 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129671725</v>
+        <v>129671399</v>
       </c>
       <c r="B10" t="n">
-        <v>91599</v>
+        <v>98780</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1590,10 +1595,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>781721</v>
+        <v>781522</v>
       </c>
       <c r="R10" t="n">
-        <v>7143412</v>
+        <v>7143269</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1620,12 +1625,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>med överblommad blomstängel</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,7 +1663,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129671399</v>
+        <v>129671431</v>
       </c>
       <c r="B11" t="n">
         <v>98780</v>
@@ -1687,11 +1697,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1700,10 +1706,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>781522</v>
+        <v>781554</v>
       </c>
       <c r="R11" t="n">
-        <v>7143269</v>
+        <v>7143299</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1736,11 +1742,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>med överblommad blomstängel</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1768,42 +1769,41 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129671431</v>
+        <v>129671725</v>
       </c>
       <c r="B12" t="n">
-        <v>98780</v>
+        <v>91599</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1811,10 +1811,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>781554</v>
+        <v>781721</v>
       </c>
       <c r="R12" t="n">
-        <v>7143299</v>
+        <v>7143412</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,12 +1841,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1874,38 +1874,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129671776</v>
+        <v>129670107</v>
       </c>
       <c r="B13" t="n">
-        <v>98780</v>
+        <v>57733</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1913,10 +1917,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>781537</v>
+        <v>781364</v>
       </c>
       <c r="R13" t="n">
-        <v>7143351</v>
+        <v>7143210</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1943,17 +1947,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ca 2 x 1 m med bladrosetter</t>
+          <t>hål i naturlig granstubbe</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1962,7 +1966,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1981,41 +1984,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129670229</v>
+        <v>129670096</v>
       </c>
       <c r="B14" t="n">
-        <v>91897</v>
+        <v>98780</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2023,10 +2027,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>781534</v>
+        <v>781314</v>
       </c>
       <c r="R14" t="n">
-        <v>7143302</v>
+        <v>7143242</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2063,7 +2067,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>på samma låga som ostticka, kötticka och ullticka</t>
+          <t>ca 1x1 meter med bladrosetter</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2091,10 +2095,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129670107</v>
+        <v>129670229</v>
       </c>
       <c r="B15" t="n">
-        <v>57733</v>
+        <v>91897</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2102,31 +2106,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2134,10 +2137,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>781364</v>
+        <v>781534</v>
       </c>
       <c r="R15" t="n">
-        <v>7143210</v>
+        <v>7143302</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2174,7 +2177,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>hål i naturlig granstubbe</t>
+          <t>på samma låga som ostticka, kötticka och ullticka</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2183,6 +2186,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2201,7 +2205,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129670096</v>
+        <v>129671776</v>
       </c>
       <c r="B16" t="n">
         <v>98780</v>
@@ -2230,11 +2234,7 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -2244,10 +2244,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>781314</v>
+        <v>781537</v>
       </c>
       <c r="R16" t="n">
-        <v>7143242</v>
+        <v>7143351</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2274,17 +2274,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ca 1x1 meter med bladrosetter</t>
+          <t>ca 2 x 1 m med bladrosetter</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -4134,41 +4134,42 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129670180</v>
+        <v>129671316</v>
       </c>
       <c r="B34" t="n">
-        <v>91981</v>
+        <v>57733</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1506</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4176,10 +4177,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>781534</v>
+        <v>781538</v>
       </c>
       <c r="R34" t="n">
-        <v>7143302</v>
+        <v>7143358</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4216,7 +4217,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>på granlåga med ullticka, kötticka och rosenticka</t>
+          <t>hål i högstubbe</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4225,7 +4226,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4244,42 +4244,42 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129671316</v>
+        <v>129671452</v>
       </c>
       <c r="B35" t="n">
-        <v>57733</v>
+        <v>98780</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4287,10 +4287,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>781538</v>
+        <v>781558</v>
       </c>
       <c r="R35" t="n">
-        <v>7143358</v>
+        <v>7143348</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4325,17 +4325,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>hål i högstubbe</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4354,10 +4350,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129671452</v>
+        <v>129670180</v>
       </c>
       <c r="B36" t="n">
-        <v>98780</v>
+        <v>91981</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4365,31 +4361,30 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>1506</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4397,10 +4392,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>781558</v>
+        <v>781534</v>
       </c>
       <c r="R36" t="n">
-        <v>7143348</v>
+        <v>7143302</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4433,6 +4428,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>på granlåga med ullticka, kötticka och rosenticka</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 48749-2025 artfynd.xlsx
+++ b/artfynd/A 48749-2025 artfynd.xlsx
@@ -3500,42 +3500,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129671659</v>
+        <v>129671572</v>
       </c>
       <c r="B28" t="n">
-        <v>98780</v>
+        <v>91619</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3543,10 +3538,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>781711</v>
+        <v>781468</v>
       </c>
       <c r="R28" t="n">
-        <v>7143272</v>
+        <v>7143208</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3606,37 +3601,42 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129671572</v>
+        <v>129671659</v>
       </c>
       <c r="B29" t="n">
-        <v>91619</v>
+        <v>98780</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3644,10 +3644,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>781468</v>
+        <v>781711</v>
       </c>
       <c r="R29" t="n">
-        <v>7143208</v>
+        <v>7143272</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 48749-2025 artfynd.xlsx
+++ b/artfynd/A 48749-2025 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>129671679</v>
       </c>
       <c r="B3" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>129671353</v>
       </c>
       <c r="B4" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>129671369</v>
       </c>
       <c r="B6" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1548,46 +1548,41 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129671399</v>
+        <v>129671725</v>
       </c>
       <c r="B10" t="n">
-        <v>98780</v>
+        <v>91599</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1595,10 +1590,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>781522</v>
+        <v>781721</v>
       </c>
       <c r="R10" t="n">
-        <v>7143269</v>
+        <v>7143412</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1625,17 +1620,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>med överblommad blomstängel</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1666,7 +1656,7 @@
         <v>129671431</v>
       </c>
       <c r="B11" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1769,41 +1759,46 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129671725</v>
+        <v>129671399</v>
       </c>
       <c r="B12" t="n">
-        <v>91599</v>
+        <v>98790</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1811,10 +1806,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>781721</v>
+        <v>781522</v>
       </c>
       <c r="R12" t="n">
-        <v>7143412</v>
+        <v>7143269</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,12 +1836,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>med överblommad blomstängel</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1874,42 +1874,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129670107</v>
+        <v>129670096</v>
       </c>
       <c r="B13" t="n">
-        <v>57733</v>
+        <v>98790</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1917,10 +1917,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>781364</v>
+        <v>781314</v>
       </c>
       <c r="R13" t="n">
-        <v>7143210</v>
+        <v>7143242</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1957,7 +1957,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>hål i naturlig granstubbe</t>
+          <t>ca 1x1 meter med bladrosetter</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1966,6 +1966,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1984,42 +1985,41 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129670096</v>
+        <v>129670229</v>
       </c>
       <c r="B14" t="n">
-        <v>98780</v>
+        <v>91897</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>781314</v>
+        <v>781534</v>
       </c>
       <c r="R14" t="n">
-        <v>7143242</v>
+        <v>7143302</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ca 1x1 meter med bladrosetter</t>
+          <t>på samma låga som ostticka, kötticka och ullticka</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2095,10 +2095,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129670229</v>
+        <v>129670107</v>
       </c>
       <c r="B15" t="n">
-        <v>91897</v>
+        <v>57733</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2106,30 +2106,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2137,10 +2138,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>781534</v>
+        <v>781364</v>
       </c>
       <c r="R15" t="n">
-        <v>7143302</v>
+        <v>7143210</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2177,7 +2178,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>på samma låga som ostticka, kötticka och ullticka</t>
+          <t>hål i naturlig granstubbe</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2186,7 +2187,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2208,7 +2208,7 @@
         <v>129671776</v>
       </c>
       <c r="B16" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2417,10 +2417,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129671643</v>
+        <v>129671583</v>
       </c>
       <c r="B18" t="n">
-        <v>91550</v>
+        <v>57733</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2428,30 +2428,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>112</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2459,10 +2460,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>781633</v>
+        <v>781512</v>
       </c>
       <c r="R18" t="n">
-        <v>7143286</v>
+        <v>7143186</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2497,13 +2498,17 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>färskt hål i tall</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2522,10 +2527,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129671583</v>
+        <v>129671643</v>
       </c>
       <c r="B19" t="n">
-        <v>57733</v>
+        <v>91550</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2533,31 +2538,30 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>112</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2565,10 +2569,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>781512</v>
+        <v>781633</v>
       </c>
       <c r="R19" t="n">
-        <v>7143186</v>
+        <v>7143286</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2603,17 +2607,13 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>färskt hål i tall</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2632,32 +2632,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129671769</v>
+        <v>129671717</v>
       </c>
       <c r="B20" t="n">
-        <v>91563</v>
+        <v>91599</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2674,10 +2674,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>781492</v>
+        <v>781823</v>
       </c>
       <c r="R20" t="n">
-        <v>7143441</v>
+        <v>7143286</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2847,32 +2847,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129671717</v>
+        <v>129671769</v>
       </c>
       <c r="B22" t="n">
-        <v>91599</v>
+        <v>91563</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>781823</v>
+        <v>781492</v>
       </c>
       <c r="R22" t="n">
-        <v>7143286</v>
+        <v>7143441</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3065,7 +3065,7 @@
         <v>129671688</v>
       </c>
       <c r="B24" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3173,42 +3173,41 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129671422</v>
+        <v>129671363</v>
       </c>
       <c r="B25" t="n">
-        <v>98780</v>
+        <v>79081</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3216,10 +3215,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>781559</v>
+        <v>781284</v>
       </c>
       <c r="R25" t="n">
-        <v>7143298</v>
+        <v>7143261</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3252,11 +3251,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>ca 2 x 2 meter med bladrosetter</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3284,41 +3278,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129671363</v>
+        <v>129671328</v>
       </c>
       <c r="B26" t="n">
-        <v>79081</v>
+        <v>98790</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3326,10 +3321,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>781284</v>
+        <v>781377</v>
       </c>
       <c r="R26" t="n">
-        <v>7143261</v>
+        <v>7143460</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3362,6 +3357,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>ca 1 x 1 meter med bladrosetter</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3389,10 +3389,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129671328</v>
+        <v>129671422</v>
       </c>
       <c r="B27" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>781377</v>
+        <v>781559</v>
       </c>
       <c r="R27" t="n">
-        <v>7143460</v>
+        <v>7143298</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>ca 1 x 1 meter med bladrosetter</t>
+          <t>ca 2 x 2 meter med bladrosetter</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3604,7 +3604,7 @@
         <v>129671659</v>
       </c>
       <c r="B29" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>129671752</v>
       </c>
       <c r="B33" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4244,10 +4244,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129671452</v>
+        <v>129670180</v>
       </c>
       <c r="B35" t="n">
-        <v>98780</v>
+        <v>91981</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4255,31 +4255,30 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>1506</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4287,10 +4286,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>781558</v>
+        <v>781534</v>
       </c>
       <c r="R35" t="n">
-        <v>7143348</v>
+        <v>7143302</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4323,6 +4322,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>på granlåga med ullticka, kötticka och rosenticka</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4350,10 +4354,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129670180</v>
+        <v>129671452</v>
       </c>
       <c r="B36" t="n">
-        <v>91981</v>
+        <v>98790</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4361,30 +4365,31 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1506</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4392,10 +4397,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>781534</v>
+        <v>781558</v>
       </c>
       <c r="R36" t="n">
-        <v>7143302</v>
+        <v>7143348</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4428,11 +4433,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>på granlåga med ullticka, kötticka och rosenticka</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 48749-2025 artfynd.xlsx
+++ b/artfynd/A 48749-2025 artfynd.xlsx
@@ -2632,10 +2632,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129671717</v>
+        <v>129671437</v>
       </c>
       <c r="B20" t="n">
-        <v>91599</v>
+        <v>82918</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2643,21 +2643,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2674,10 +2674,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>781823</v>
+        <v>781567</v>
       </c>
       <c r="R20" t="n">
-        <v>7143286</v>
+        <v>7143316</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2704,12 +2704,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>på krokig gammelgran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2737,32 +2742,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129671437</v>
+        <v>129671769</v>
       </c>
       <c r="B21" t="n">
-        <v>82918</v>
+        <v>91563</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2779,10 +2784,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>781567</v>
+        <v>781492</v>
       </c>
       <c r="R21" t="n">
-        <v>7143316</v>
+        <v>7143441</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2809,17 +2814,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>på krokig gammelgran</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2847,41 +2847,42 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129671769</v>
+        <v>129671522</v>
       </c>
       <c r="B22" t="n">
-        <v>91563</v>
+        <v>57733</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2889,10 +2890,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>781492</v>
+        <v>781374</v>
       </c>
       <c r="R22" t="n">
-        <v>7143441</v>
+        <v>7143326</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2919,12 +2920,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>färska hål i gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2933,7 +2939,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2952,10 +2957,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129671522</v>
+        <v>129671717</v>
       </c>
       <c r="B23" t="n">
-        <v>57733</v>
+        <v>91599</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2963,31 +2968,30 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2995,10 +2999,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>781374</v>
+        <v>781823</v>
       </c>
       <c r="R23" t="n">
-        <v>7143326</v>
+        <v>7143286</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3025,17 +3029,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>färska hål i gran</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3044,6 +3043,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3707,10 +3707,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129671514</v>
+        <v>129671632</v>
       </c>
       <c r="B30" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3718,16 +3718,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3738,11 +3738,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3750,10 +3746,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>781563</v>
+        <v>781623</v>
       </c>
       <c r="R30" t="n">
-        <v>7143446</v>
+        <v>7143270</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3780,17 +3776,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>färska hål</t>
+          <t>gammalt bohål i granlåga, rätt storlek för tretåig hackspett</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3817,10 +3813,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129671632</v>
+        <v>129671514</v>
       </c>
       <c r="B31" t="n">
-        <v>57736</v>
+        <v>57733</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3828,16 +3824,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3848,7 +3844,11 @@
       <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3856,10 +3856,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>781623</v>
+        <v>781563</v>
       </c>
       <c r="R31" t="n">
-        <v>7143270</v>
+        <v>7143446</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3886,17 +3886,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>gammalt bohål i granlåga, rätt storlek för tretåig hackspett</t>
+          <t>färska hål</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 48749-2025 artfynd.xlsx
+++ b/artfynd/A 48749-2025 artfynd.xlsx
@@ -997,42 +997,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129671604</v>
+        <v>129671369</v>
       </c>
       <c r="B5" t="n">
-        <v>57733</v>
+        <v>98790</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>781583</v>
+        <v>781313</v>
       </c>
       <c r="R5" t="n">
-        <v>7143145</v>
+        <v>7143250</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1070,17 +1070,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>hack i låga</t>
+          <t>ca 1 x 3 meter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1089,6 +1089,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1107,42 +1108,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129671369</v>
+        <v>129671604</v>
       </c>
       <c r="B6" t="n">
-        <v>98790</v>
+        <v>57733</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1150,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>781313</v>
+        <v>781583</v>
       </c>
       <c r="R6" t="n">
-        <v>7143250</v>
+        <v>7143145</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,17 +1181,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ca 1 x 3 meter med bladrosetter!</t>
+          <t>hack i låga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1199,7 +1200,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -2417,10 +2417,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129671583</v>
+        <v>129671643</v>
       </c>
       <c r="B18" t="n">
-        <v>57733</v>
+        <v>91550</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2428,31 +2428,30 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>112</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2460,10 +2459,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>781512</v>
+        <v>781633</v>
       </c>
       <c r="R18" t="n">
-        <v>7143186</v>
+        <v>7143286</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2498,17 +2497,13 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>färskt hål i tall</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2527,10 +2522,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129671643</v>
+        <v>129671583</v>
       </c>
       <c r="B19" t="n">
-        <v>91550</v>
+        <v>57733</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2538,30 +2533,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>112</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2569,10 +2565,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>781633</v>
+        <v>781512</v>
       </c>
       <c r="R19" t="n">
-        <v>7143286</v>
+        <v>7143186</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2607,13 +2603,17 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>färskt hål i tall</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129671437</v>
+        <v>129671717</v>
       </c>
       <c r="B20" t="n">
-        <v>82918</v>
+        <v>91599</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2643,21 +2643,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2674,10 +2674,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>781567</v>
+        <v>781823</v>
       </c>
       <c r="R20" t="n">
-        <v>7143316</v>
+        <v>7143286</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2704,17 +2704,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>på krokig gammelgran</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2742,32 +2737,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129671769</v>
+        <v>129671437</v>
       </c>
       <c r="B21" t="n">
-        <v>91563</v>
+        <v>82918</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2784,10 +2779,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>781492</v>
+        <v>781567</v>
       </c>
       <c r="R21" t="n">
-        <v>7143441</v>
+        <v>7143316</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2814,12 +2809,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>på krokig gammelgran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2847,42 +2847,41 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129671522</v>
+        <v>129671769</v>
       </c>
       <c r="B22" t="n">
-        <v>57733</v>
+        <v>91563</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2890,10 +2889,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>781374</v>
+        <v>781492</v>
       </c>
       <c r="R22" t="n">
-        <v>7143326</v>
+        <v>7143441</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2920,17 +2919,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>färska hål i gran</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2939,6 +2933,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2957,10 +2952,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129671717</v>
+        <v>129671522</v>
       </c>
       <c r="B23" t="n">
-        <v>91599</v>
+        <v>57733</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2968,30 +2963,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2999,10 +2995,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>781823</v>
+        <v>781374</v>
       </c>
       <c r="R23" t="n">
-        <v>7143286</v>
+        <v>7143326</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3029,12 +3025,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>färska hål i gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3043,7 +3044,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -4134,42 +4134,41 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129671316</v>
+        <v>129670180</v>
       </c>
       <c r="B34" t="n">
-        <v>57733</v>
+        <v>91981</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>1506</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4177,10 +4176,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>781538</v>
+        <v>781534</v>
       </c>
       <c r="R34" t="n">
-        <v>7143358</v>
+        <v>7143302</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4217,7 +4216,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>hål i högstubbe</t>
+          <t>på granlåga med ullticka, kötticka och rosenticka</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4226,6 +4225,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4244,10 +4244,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129670180</v>
+        <v>129671452</v>
       </c>
       <c r="B35" t="n">
-        <v>91981</v>
+        <v>98790</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4255,30 +4255,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1506</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4286,10 +4287,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>781534</v>
+        <v>781558</v>
       </c>
       <c r="R35" t="n">
-        <v>7143302</v>
+        <v>7143348</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4322,11 +4323,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>på granlåga med ullticka, kötticka och rosenticka</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4354,42 +4350,42 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129671452</v>
+        <v>129671316</v>
       </c>
       <c r="B36" t="n">
-        <v>98790</v>
+        <v>57733</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4397,10 +4393,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>781558</v>
+        <v>781538</v>
       </c>
       <c r="R36" t="n">
-        <v>7143348</v>
+        <v>7143358</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4435,13 +4431,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>hål i högstubbe</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 48749-2025 artfynd.xlsx
+++ b/artfynd/A 48749-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129671611</v>
       </c>
       <c r="B2" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>129671679</v>
       </c>
       <c r="B3" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>129671353</v>
       </c>
       <c r="B4" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>129671369</v>
       </c>
       <c r="B5" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>129671604</v>
       </c>
       <c r="B6" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>129671322</v>
       </c>
       <c r="B7" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>129671307</v>
       </c>
       <c r="B8" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>129670173</v>
       </c>
       <c r="B9" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>129671725</v>
       </c>
       <c r="B10" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>129671431</v>
       </c>
       <c r="B11" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>129671399</v>
       </c>
       <c r="B12" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1874,10 +1874,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129670096</v>
+        <v>129671776</v>
       </c>
       <c r="B13" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1903,11 +1903,7 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -1917,10 +1913,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>781314</v>
+        <v>781537</v>
       </c>
       <c r="R13" t="n">
-        <v>7143242</v>
+        <v>7143351</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,17 +1943,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ca 1x1 meter med bladrosetter</t>
+          <t>ca 2 x 1 m med bladrosetter</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1985,41 +1981,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129670229</v>
+        <v>129670096</v>
       </c>
       <c r="B14" t="n">
-        <v>91897</v>
+        <v>98794</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2027,10 +2024,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>781534</v>
+        <v>781314</v>
       </c>
       <c r="R14" t="n">
-        <v>7143302</v>
+        <v>7143242</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2067,7 +2064,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>på samma låga som ostticka, kötticka och ullticka</t>
+          <t>ca 1x1 meter med bladrosetter</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2095,10 +2092,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129670107</v>
+        <v>129670229</v>
       </c>
       <c r="B15" t="n">
-        <v>57733</v>
+        <v>91900</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2106,31 +2103,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2138,10 +2134,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>781364</v>
+        <v>781534</v>
       </c>
       <c r="R15" t="n">
-        <v>7143210</v>
+        <v>7143302</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2178,7 +2174,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>hål i naturlig granstubbe</t>
+          <t>på samma låga som ostticka, kötticka och ullticka</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2187,6 +2183,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2205,38 +2202,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129671776</v>
+        <v>129670107</v>
       </c>
       <c r="B16" t="n">
-        <v>98790</v>
+        <v>57734</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2244,10 +2245,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>781537</v>
+        <v>781364</v>
       </c>
       <c r="R16" t="n">
-        <v>7143351</v>
+        <v>7143210</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2274,17 +2275,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ca 2 x 1 m med bladrosetter</t>
+          <t>hål i naturlig granstubbe</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2293,7 +2294,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2315,7 +2315,7 @@
         <v>129671733</v>
       </c>
       <c r="B17" t="n">
-        <v>82918</v>
+        <v>82921</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>129671643</v>
       </c>
       <c r="B18" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>129671583</v>
       </c>
       <c r="B19" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129671717</v>
+        <v>129671437</v>
       </c>
       <c r="B20" t="n">
-        <v>91599</v>
+        <v>82921</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2643,21 +2643,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2674,10 +2674,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>781823</v>
+        <v>781567</v>
       </c>
       <c r="R20" t="n">
-        <v>7143286</v>
+        <v>7143316</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2704,12 +2704,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>på krokig gammelgran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2737,10 +2742,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129671437</v>
+        <v>129671717</v>
       </c>
       <c r="B21" t="n">
-        <v>82918</v>
+        <v>91602</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2748,21 +2753,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2779,10 +2784,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>781567</v>
+        <v>781823</v>
       </c>
       <c r="R21" t="n">
-        <v>7143316</v>
+        <v>7143286</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2809,17 +2814,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>på krokig gammelgran</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2850,7 +2850,7 @@
         <v>129671769</v>
       </c>
       <c r="B22" t="n">
-        <v>91563</v>
+        <v>91566</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>129671522</v>
       </c>
       <c r="B23" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3065,7 +3065,7 @@
         <v>129671688</v>
       </c>
       <c r="B24" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>129671363</v>
       </c>
       <c r="B25" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>129671328</v>
       </c>
       <c r="B26" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>129671422</v>
       </c>
       <c r="B27" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>129671572</v>
       </c>
       <c r="B28" t="n">
-        <v>91619</v>
+        <v>91622</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         <v>129671659</v>
       </c>
       <c r="B29" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3707,10 +3707,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129671632</v>
+        <v>129671514</v>
       </c>
       <c r="B30" t="n">
-        <v>57736</v>
+        <v>57734</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3718,16 +3718,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3738,7 +3738,11 @@
       <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3746,10 +3750,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>781623</v>
+        <v>781563</v>
       </c>
       <c r="R30" t="n">
-        <v>7143270</v>
+        <v>7143446</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3776,17 +3780,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>gammalt bohål i granlåga, rätt storlek för tretåig hackspett</t>
+          <t>färska hål</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3813,10 +3817,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129671514</v>
+        <v>129671632</v>
       </c>
       <c r="B31" t="n">
-        <v>57733</v>
+        <v>57737</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3824,16 +3828,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3844,11 +3848,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3856,10 +3856,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>781563</v>
+        <v>781623</v>
       </c>
       <c r="R31" t="n">
-        <v>7143446</v>
+        <v>7143270</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3886,17 +3886,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>färska hål</t>
+          <t>gammalt bohål i granlåga, rätt storlek för tretåig hackspett</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3926,7 +3926,7 @@
         <v>129671647</v>
       </c>
       <c r="B32" t="n">
-        <v>82918</v>
+        <v>82921</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>129671752</v>
       </c>
       <c r="B33" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4137,7 +4137,7 @@
         <v>129670180</v>
       </c>
       <c r="B34" t="n">
-        <v>91981</v>
+        <v>91984</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4244,42 +4244,42 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129671452</v>
+        <v>129671316</v>
       </c>
       <c r="B35" t="n">
-        <v>98790</v>
+        <v>57734</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4287,10 +4287,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>781558</v>
+        <v>781538</v>
       </c>
       <c r="R35" t="n">
-        <v>7143348</v>
+        <v>7143358</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4325,13 +4325,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>hål i högstubbe</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4350,42 +4354,42 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129671316</v>
+        <v>129671452</v>
       </c>
       <c r="B36" t="n">
-        <v>57733</v>
+        <v>98794</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4393,10 +4397,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>781538</v>
+        <v>781558</v>
       </c>
       <c r="R36" t="n">
-        <v>7143358</v>
+        <v>7143348</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4431,17 +4435,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>hål i högstubbe</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 48749-2025 artfynd.xlsx
+++ b/artfynd/A 48749-2025 artfynd.xlsx
@@ -997,42 +997,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129671369</v>
+        <v>129671604</v>
       </c>
       <c r="B5" t="n">
-        <v>98794</v>
+        <v>57734</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>781313</v>
+        <v>781583</v>
       </c>
       <c r="R5" t="n">
-        <v>7143250</v>
+        <v>7143145</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1070,17 +1070,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ca 1 x 3 meter med bladrosetter!</t>
+          <t>hack i låga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1089,7 +1089,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1108,42 +1107,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129671604</v>
+        <v>129671369</v>
       </c>
       <c r="B6" t="n">
-        <v>57734</v>
+        <v>98794</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1151,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>781583</v>
+        <v>781313</v>
       </c>
       <c r="R6" t="n">
-        <v>7143145</v>
+        <v>7143250</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,17 +1180,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>hack i låga</t>
+          <t>ca 1 x 3 meter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,6 +1199,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1548,41 +1548,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129671725</v>
+        <v>129671431</v>
       </c>
       <c r="B10" t="n">
-        <v>91602</v>
+        <v>98794</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1590,10 +1591,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>781721</v>
+        <v>781554</v>
       </c>
       <c r="R10" t="n">
-        <v>7143412</v>
+        <v>7143299</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1620,12 +1621,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,7 +1654,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129671431</v>
+        <v>129671399</v>
       </c>
       <c r="B11" t="n">
         <v>98794</v>
@@ -1687,7 +1688,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1696,10 +1701,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>781554</v>
+        <v>781522</v>
       </c>
       <c r="R11" t="n">
-        <v>7143299</v>
+        <v>7143269</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1732,6 +1737,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>med överblommad blomstängel</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1759,46 +1769,41 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129671399</v>
+        <v>129671725</v>
       </c>
       <c r="B12" t="n">
-        <v>98794</v>
+        <v>91602</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1806,10 +1811,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>781522</v>
+        <v>781721</v>
       </c>
       <c r="R12" t="n">
-        <v>7143269</v>
+        <v>7143412</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1836,17 +1841,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>med överblommad blomstängel</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1874,38 +1874,41 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129671776</v>
+        <v>129670229</v>
       </c>
       <c r="B13" t="n">
-        <v>98794</v>
+        <v>91900</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1913,10 +1916,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>781537</v>
+        <v>781534</v>
       </c>
       <c r="R13" t="n">
-        <v>7143351</v>
+        <v>7143302</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1943,17 +1946,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ca 2 x 1 m med bladrosetter</t>
+          <t>på samma låga som ostticka, kötticka och ullticka</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1981,42 +1984,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129670096</v>
+        <v>129670107</v>
       </c>
       <c r="B14" t="n">
-        <v>98794</v>
+        <v>57734</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2024,10 +2027,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>781314</v>
+        <v>781364</v>
       </c>
       <c r="R14" t="n">
-        <v>7143242</v>
+        <v>7143210</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2064,7 +2067,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ca 1x1 meter med bladrosetter</t>
+          <t>hål i naturlig granstubbe</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2073,7 +2076,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2092,41 +2094,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129670229</v>
+        <v>129671776</v>
       </c>
       <c r="B15" t="n">
-        <v>91900</v>
+        <v>98794</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2134,10 +2133,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>781534</v>
+        <v>781537</v>
       </c>
       <c r="R15" t="n">
-        <v>7143302</v>
+        <v>7143351</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2164,17 +2163,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>på samma låga som ostticka, kötticka och ullticka</t>
+          <t>ca 2 x 1 m med bladrosetter</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2202,42 +2201,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129670107</v>
+        <v>129670096</v>
       </c>
       <c r="B16" t="n">
-        <v>57734</v>
+        <v>98794</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2245,10 +2244,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>781364</v>
+        <v>781314</v>
       </c>
       <c r="R16" t="n">
-        <v>7143210</v>
+        <v>7143242</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2285,7 +2284,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>hål i naturlig granstubbe</t>
+          <t>ca 1x1 meter med bladrosetter</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2294,6 +2293,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -3707,10 +3707,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129671514</v>
+        <v>129671632</v>
       </c>
       <c r="B30" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3718,16 +3718,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3738,11 +3738,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3750,10 +3746,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>781563</v>
+        <v>781623</v>
       </c>
       <c r="R30" t="n">
-        <v>7143446</v>
+        <v>7143270</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3780,17 +3776,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>färska hål</t>
+          <t>gammalt bohål i granlåga, rätt storlek för tretåig hackspett</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3817,10 +3813,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129671632</v>
+        <v>129671514</v>
       </c>
       <c r="B31" t="n">
-        <v>57737</v>
+        <v>57734</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3828,16 +3824,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3848,7 +3844,11 @@
       <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3856,10 +3856,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>781623</v>
+        <v>781563</v>
       </c>
       <c r="R31" t="n">
-        <v>7143270</v>
+        <v>7143446</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3886,17 +3886,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>gammalt bohål i granlåga, rätt storlek för tretåig hackspett</t>
+          <t>färska hål</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 48749-2025 artfynd.xlsx
+++ b/artfynd/A 48749-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129671611</v>
       </c>
       <c r="B2" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>129671679</v>
       </c>
       <c r="B3" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>129671353</v>
       </c>
       <c r="B4" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>129671604</v>
       </c>
       <c r="B5" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>129671369</v>
       </c>
       <c r="B6" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>129671322</v>
       </c>
       <c r="B7" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>129671307</v>
       </c>
       <c r="B8" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>129670173</v>
       </c>
       <c r="B9" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,42 +1548,41 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129671431</v>
+        <v>129671725</v>
       </c>
       <c r="B10" t="n">
-        <v>98794</v>
+        <v>91605</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1591,10 +1590,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>781554</v>
+        <v>781721</v>
       </c>
       <c r="R10" t="n">
-        <v>7143299</v>
+        <v>7143412</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1621,12 +1620,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1654,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129671399</v>
+        <v>129671431</v>
       </c>
       <c r="B11" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,11 +1687,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1701,10 +1696,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>781522</v>
+        <v>781554</v>
       </c>
       <c r="R11" t="n">
-        <v>7143269</v>
+        <v>7143299</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1737,11 +1732,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>med överblommad blomstängel</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1769,41 +1759,46 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129671725</v>
+        <v>129671399</v>
       </c>
       <c r="B12" t="n">
-        <v>91602</v>
+        <v>98797</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1811,10 +1806,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>781721</v>
+        <v>781522</v>
       </c>
       <c r="R12" t="n">
-        <v>7143412</v>
+        <v>7143269</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,12 +1836,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>med överblommad blomstängel</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1877,7 +1877,7 @@
         <v>129670229</v>
       </c>
       <c r="B13" t="n">
-        <v>91900</v>
+        <v>91903</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>129670107</v>
       </c>
       <c r="B14" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>129671776</v>
       </c>
       <c r="B15" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>129670096</v>
       </c>
       <c r="B16" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>129671733</v>
       </c>
       <c r="B17" t="n">
-        <v>82921</v>
+        <v>82924</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>129671643</v>
       </c>
       <c r="B18" t="n">
-        <v>91553</v>
+        <v>91556</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>129671583</v>
       </c>
       <c r="B19" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2632,41 +2632,42 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129671437</v>
+        <v>129671688</v>
       </c>
       <c r="B20" t="n">
-        <v>82921</v>
+        <v>98797</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2674,10 +2675,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>781567</v>
+        <v>781774</v>
       </c>
       <c r="R20" t="n">
-        <v>7143316</v>
+        <v>7143251</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2704,17 +2705,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>på krokig gammelgran</t>
+          <t>3 x 1 meter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2742,10 +2743,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129671717</v>
+        <v>129671437</v>
       </c>
       <c r="B21" t="n">
-        <v>91602</v>
+        <v>82924</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2753,21 +2754,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2784,10 +2785,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>781823</v>
+        <v>781567</v>
       </c>
       <c r="R21" t="n">
-        <v>7143286</v>
+        <v>7143316</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2814,12 +2815,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>på krokig gammelgran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2850,7 +2856,7 @@
         <v>129671769</v>
       </c>
       <c r="B22" t="n">
-        <v>91566</v>
+        <v>91569</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2952,10 +2958,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129671522</v>
+        <v>129671717</v>
       </c>
       <c r="B23" t="n">
-        <v>57734</v>
+        <v>91605</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2963,31 +2969,30 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2995,10 +3000,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>781374</v>
+        <v>781823</v>
       </c>
       <c r="R23" t="n">
-        <v>7143326</v>
+        <v>7143286</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3025,17 +3030,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>färska hål i gran</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3044,6 +3044,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3062,42 +3063,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129671688</v>
+        <v>129671522</v>
       </c>
       <c r="B24" t="n">
-        <v>98794</v>
+        <v>57737</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3105,10 +3106,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>781774</v>
+        <v>781374</v>
       </c>
       <c r="R24" t="n">
-        <v>7143251</v>
+        <v>7143326</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3135,17 +3136,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>3 x 1 meter med bladrosetter!</t>
+          <t>färska hål i gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3154,7 +3155,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3173,41 +3173,42 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129671363</v>
+        <v>129671328</v>
       </c>
       <c r="B25" t="n">
-        <v>79084</v>
+        <v>98797</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3215,10 +3216,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>781284</v>
+        <v>781377</v>
       </c>
       <c r="R25" t="n">
-        <v>7143261</v>
+        <v>7143460</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3251,6 +3252,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>ca 1 x 1 meter med bladrosetter</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3278,10 +3284,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129671328</v>
+        <v>129671422</v>
       </c>
       <c r="B26" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3321,10 +3327,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>781377</v>
+        <v>781559</v>
       </c>
       <c r="R26" t="n">
-        <v>7143460</v>
+        <v>7143298</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3361,7 +3367,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>ca 1 x 1 meter med bladrosetter</t>
+          <t>ca 2 x 2 meter med bladrosetter</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3389,42 +3395,41 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129671422</v>
+        <v>129671363</v>
       </c>
       <c r="B27" t="n">
-        <v>98794</v>
+        <v>79087</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3432,10 +3437,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>781559</v>
+        <v>781284</v>
       </c>
       <c r="R27" t="n">
-        <v>7143298</v>
+        <v>7143261</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3468,11 +3473,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>ca 2 x 2 meter med bladrosetter</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3503,7 +3503,7 @@
         <v>129671572</v>
       </c>
       <c r="B28" t="n">
-        <v>91622</v>
+        <v>91625</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         <v>129671659</v>
       </c>
       <c r="B29" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129671632</v>
+        <v>129671514</v>
       </c>
       <c r="B30" t="n">
         <v>57737</v>
@@ -3718,16 +3718,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3738,7 +3738,11 @@
       <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3746,10 +3750,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>781623</v>
+        <v>781563</v>
       </c>
       <c r="R30" t="n">
-        <v>7143270</v>
+        <v>7143446</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3776,17 +3780,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>gammalt bohål i granlåga, rätt storlek för tretåig hackspett</t>
+          <t>färska hål</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3813,10 +3817,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129671514</v>
+        <v>129671632</v>
       </c>
       <c r="B31" t="n">
-        <v>57734</v>
+        <v>57740</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3824,16 +3828,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3844,11 +3848,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3856,10 +3856,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>781563</v>
+        <v>781623</v>
       </c>
       <c r="R31" t="n">
-        <v>7143446</v>
+        <v>7143270</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3886,17 +3886,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>färska hål</t>
+          <t>gammalt bohål i granlåga, rätt storlek för tretåig hackspett</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3926,7 +3926,7 @@
         <v>129671647</v>
       </c>
       <c r="B32" t="n">
-        <v>82921</v>
+        <v>82924</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>129671752</v>
       </c>
       <c r="B33" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4134,41 +4134,42 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129670180</v>
+        <v>129671316</v>
       </c>
       <c r="B34" t="n">
-        <v>91984</v>
+        <v>57737</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1506</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4176,10 +4177,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>781534</v>
+        <v>781538</v>
       </c>
       <c r="R34" t="n">
-        <v>7143302</v>
+        <v>7143358</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4216,7 +4217,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>på granlåga med ullticka, kötticka och rosenticka</t>
+          <t>hål i högstubbe</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4225,7 +4226,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4244,42 +4244,41 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129671316</v>
+        <v>129670180</v>
       </c>
       <c r="B35" t="n">
-        <v>57734</v>
+        <v>91987</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>1506</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4287,10 +4286,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>781538</v>
+        <v>781534</v>
       </c>
       <c r="R35" t="n">
-        <v>7143358</v>
+        <v>7143302</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4327,7 +4326,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>hål i högstubbe</t>
+          <t>på granlåga med ullticka, kötticka och rosenticka</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4336,6 +4335,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4357,7 +4357,7 @@
         <v>129671452</v>
       </c>
       <c r="B36" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 48749-2025 artfynd.xlsx
+++ b/artfynd/A 48749-2025 artfynd.xlsx
@@ -1548,41 +1548,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129671725</v>
+        <v>129671431</v>
       </c>
       <c r="B10" t="n">
-        <v>91605</v>
+        <v>98797</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1590,10 +1591,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>781721</v>
+        <v>781554</v>
       </c>
       <c r="R10" t="n">
-        <v>7143412</v>
+        <v>7143299</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1620,12 +1621,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,7 +1654,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129671431</v>
+        <v>129671399</v>
       </c>
       <c r="B11" t="n">
         <v>98797</v>
@@ -1687,7 +1688,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1696,10 +1701,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>781554</v>
+        <v>781522</v>
       </c>
       <c r="R11" t="n">
-        <v>7143299</v>
+        <v>7143269</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1732,6 +1737,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>med överblommad blomstängel</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1759,46 +1769,41 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129671399</v>
+        <v>129671725</v>
       </c>
       <c r="B12" t="n">
-        <v>98797</v>
+        <v>91605</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1806,10 +1811,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>781522</v>
+        <v>781721</v>
       </c>
       <c r="R12" t="n">
-        <v>7143269</v>
+        <v>7143412</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1836,17 +1841,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>med överblommad blomstängel</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1984,42 +1984,38 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129670107</v>
+        <v>129671776</v>
       </c>
       <c r="B14" t="n">
-        <v>57737</v>
+        <v>98797</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2027,10 +2023,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>781364</v>
+        <v>781537</v>
       </c>
       <c r="R14" t="n">
-        <v>7143210</v>
+        <v>7143351</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2057,17 +2053,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>hål i naturlig granstubbe</t>
+          <t>ca 2 x 1 m med bladrosetter</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2076,6 +2072,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2094,7 +2091,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129671776</v>
+        <v>129670096</v>
       </c>
       <c r="B15" t="n">
         <v>98797</v>
@@ -2123,7 +2120,11 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -2133,10 +2134,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>781537</v>
+        <v>781314</v>
       </c>
       <c r="R15" t="n">
-        <v>7143351</v>
+        <v>7143242</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2163,17 +2164,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ca 2 x 1 m med bladrosetter</t>
+          <t>ca 1x1 meter med bladrosetter</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2201,42 +2202,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129670096</v>
+        <v>129670107</v>
       </c>
       <c r="B16" t="n">
-        <v>98797</v>
+        <v>57737</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2244,10 +2245,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>781314</v>
+        <v>781364</v>
       </c>
       <c r="R16" t="n">
-        <v>7143242</v>
+        <v>7143210</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2284,7 +2285,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ca 1x1 meter med bladrosetter</t>
+          <t>hål i naturlig granstubbe</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2293,7 +2294,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2632,42 +2632,42 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129671688</v>
+        <v>129671522</v>
       </c>
       <c r="B20" t="n">
-        <v>98797</v>
+        <v>57737</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2675,10 +2675,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>781774</v>
+        <v>781374</v>
       </c>
       <c r="R20" t="n">
-        <v>7143251</v>
+        <v>7143326</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2705,17 +2705,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>3 x 1 meter med bladrosetter!</t>
+          <t>färska hål i gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2724,7 +2724,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2743,41 +2742,42 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129671437</v>
+        <v>129671688</v>
       </c>
       <c r="B21" t="n">
-        <v>82924</v>
+        <v>98797</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2785,10 +2785,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>781567</v>
+        <v>781774</v>
       </c>
       <c r="R21" t="n">
-        <v>7143316</v>
+        <v>7143251</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2815,17 +2815,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>på krokig gammelgran</t>
+          <t>3 x 1 meter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2853,32 +2853,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129671769</v>
+        <v>129671437</v>
       </c>
       <c r="B22" t="n">
-        <v>91569</v>
+        <v>82924</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2895,10 +2895,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>781492</v>
+        <v>781567</v>
       </c>
       <c r="R22" t="n">
-        <v>7143441</v>
+        <v>7143316</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2925,12 +2925,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>på krokig gammelgran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2958,32 +2963,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129671717</v>
+        <v>129671769</v>
       </c>
       <c r="B23" t="n">
-        <v>91605</v>
+        <v>91569</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3000,10 +3005,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>781823</v>
+        <v>781492</v>
       </c>
       <c r="R23" t="n">
-        <v>7143286</v>
+        <v>7143441</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3063,10 +3068,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129671522</v>
+        <v>129671717</v>
       </c>
       <c r="B24" t="n">
-        <v>57737</v>
+        <v>91605</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3074,31 +3079,30 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3106,10 +3110,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>781374</v>
+        <v>781823</v>
       </c>
       <c r="R24" t="n">
-        <v>7143326</v>
+        <v>7143286</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3136,17 +3140,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>färska hål i gran</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3155,6 +3154,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 48749-2025 artfynd.xlsx
+++ b/artfynd/A 48749-2025 artfynd.xlsx
@@ -1984,38 +1984,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129671776</v>
+        <v>129670107</v>
       </c>
       <c r="B14" t="n">
-        <v>98797</v>
+        <v>57737</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2023,10 +2027,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>781537</v>
+        <v>781364</v>
       </c>
       <c r="R14" t="n">
-        <v>7143351</v>
+        <v>7143210</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,17 +2057,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ca 2 x 1 m med bladrosetter</t>
+          <t>hål i naturlig granstubbe</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2072,7 +2076,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2091,7 +2094,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129670096</v>
+        <v>129671776</v>
       </c>
       <c r="B15" t="n">
         <v>98797</v>
@@ -2120,11 +2123,7 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -2134,10 +2133,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>781314</v>
+        <v>781537</v>
       </c>
       <c r="R15" t="n">
-        <v>7143242</v>
+        <v>7143351</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2164,17 +2163,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ca 1x1 meter med bladrosetter</t>
+          <t>ca 2 x 1 m med bladrosetter</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2202,42 +2201,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129670107</v>
+        <v>129670096</v>
       </c>
       <c r="B16" t="n">
-        <v>57737</v>
+        <v>98797</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2245,10 +2244,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>781364</v>
+        <v>781314</v>
       </c>
       <c r="R16" t="n">
-        <v>7143210</v>
+        <v>7143242</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2285,7 +2284,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>hål i naturlig granstubbe</t>
+          <t>ca 1x1 meter med bladrosetter</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2294,6 +2293,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 48749-2025 artfynd.xlsx
+++ b/artfynd/A 48749-2025 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>129671679</v>
       </c>
       <c r="B3" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>129671353</v>
       </c>
       <c r="B4" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,42 +997,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129671604</v>
+        <v>129671369</v>
       </c>
       <c r="B5" t="n">
-        <v>57737</v>
+        <v>98798</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>781583</v>
+        <v>781313</v>
       </c>
       <c r="R5" t="n">
-        <v>7143145</v>
+        <v>7143250</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1070,17 +1070,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>hack i låga</t>
+          <t>ca 1 x 3 meter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1089,6 +1089,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1107,42 +1108,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129671369</v>
+        <v>129671604</v>
       </c>
       <c r="B6" t="n">
-        <v>98797</v>
+        <v>57737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1150,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>781313</v>
+        <v>781583</v>
       </c>
       <c r="R6" t="n">
-        <v>7143250</v>
+        <v>7143145</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,17 +1181,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ca 1 x 3 meter med bladrosetter!</t>
+          <t>hack i låga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1199,7 +1200,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1441,7 +1441,7 @@
         <v>129670173</v>
       </c>
       <c r="B9" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>129671431</v>
       </c>
       <c r="B10" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>129671399</v>
       </c>
       <c r="B11" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>129671725</v>
       </c>
       <c r="B12" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>129670229</v>
       </c>
       <c r="B13" t="n">
-        <v>91903</v>
+        <v>91904</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>129671776</v>
       </c>
       <c r="B15" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>129670096</v>
       </c>
       <c r="B16" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>129671733</v>
       </c>
       <c r="B17" t="n">
-        <v>82924</v>
+        <v>82925</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2417,10 +2417,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129671643</v>
+        <v>129671583</v>
       </c>
       <c r="B18" t="n">
-        <v>91556</v>
+        <v>57737</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2428,30 +2428,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>112</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2459,10 +2460,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>781633</v>
+        <v>781512</v>
       </c>
       <c r="R18" t="n">
-        <v>7143286</v>
+        <v>7143186</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2497,13 +2498,17 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>färskt hål i tall</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2522,10 +2527,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129671583</v>
+        <v>129671643</v>
       </c>
       <c r="B19" t="n">
-        <v>57737</v>
+        <v>91557</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2533,31 +2538,30 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>112</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2565,10 +2569,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>781512</v>
+        <v>781633</v>
       </c>
       <c r="R19" t="n">
-        <v>7143186</v>
+        <v>7143286</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2603,17 +2607,13 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>färskt hål i tall</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2742,42 +2742,41 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129671688</v>
+        <v>129671437</v>
       </c>
       <c r="B21" t="n">
-        <v>98797</v>
+        <v>82925</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2785,10 +2784,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>781774</v>
+        <v>781567</v>
       </c>
       <c r="R21" t="n">
-        <v>7143251</v>
+        <v>7143316</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2815,17 +2814,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>3 x 1 meter med bladrosetter!</t>
+          <t>på krokig gammelgran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2853,10 +2852,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129671437</v>
+        <v>129671717</v>
       </c>
       <c r="B22" t="n">
-        <v>82924</v>
+        <v>91606</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2864,21 +2863,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2895,10 +2894,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>781567</v>
+        <v>781823</v>
       </c>
       <c r="R22" t="n">
-        <v>7143316</v>
+        <v>7143286</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2925,17 +2924,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>på krokig gammelgran</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2966,7 +2960,7 @@
         <v>129671769</v>
       </c>
       <c r="B23" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3068,41 +3062,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129671717</v>
+        <v>129671688</v>
       </c>
       <c r="B24" t="n">
-        <v>91605</v>
+        <v>98798</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3110,10 +3105,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>781823</v>
+        <v>781774</v>
       </c>
       <c r="R24" t="n">
-        <v>7143286</v>
+        <v>7143251</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3146,6 +3141,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>3 x 1 meter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3173,42 +3173,41 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129671328</v>
+        <v>129671363</v>
       </c>
       <c r="B25" t="n">
-        <v>98797</v>
+        <v>79088</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3216,10 +3215,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>781377</v>
+        <v>781284</v>
       </c>
       <c r="R25" t="n">
-        <v>7143460</v>
+        <v>7143261</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3252,11 +3251,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>ca 1 x 1 meter med bladrosetter</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3284,10 +3278,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129671422</v>
+        <v>129671328</v>
       </c>
       <c r="B26" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3327,10 +3321,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>781559</v>
+        <v>781377</v>
       </c>
       <c r="R26" t="n">
-        <v>7143298</v>
+        <v>7143460</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3367,7 +3361,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>ca 2 x 2 meter med bladrosetter</t>
+          <t>ca 1 x 1 meter med bladrosetter</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3395,41 +3389,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129671363</v>
+        <v>129671422</v>
       </c>
       <c r="B27" t="n">
-        <v>79087</v>
+        <v>98798</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3437,10 +3432,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>781284</v>
+        <v>781559</v>
       </c>
       <c r="R27" t="n">
-        <v>7143261</v>
+        <v>7143298</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3473,6 +3468,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>ca 2 x 2 meter med bladrosetter</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3503,7 +3503,7 @@
         <v>129671572</v>
       </c>
       <c r="B28" t="n">
-        <v>91625</v>
+        <v>91626</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         <v>129671659</v>
       </c>
       <c r="B29" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3707,10 +3707,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129671514</v>
+        <v>129671632</v>
       </c>
       <c r="B30" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3718,16 +3718,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3738,11 +3738,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3750,10 +3746,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>781563</v>
+        <v>781623</v>
       </c>
       <c r="R30" t="n">
-        <v>7143446</v>
+        <v>7143270</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3780,17 +3776,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>färska hål</t>
+          <t>gammalt bohål i granlåga, rätt storlek för tretåig hackspett</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3817,10 +3813,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129671632</v>
+        <v>129671514</v>
       </c>
       <c r="B31" t="n">
-        <v>57740</v>
+        <v>57737</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3828,16 +3824,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3848,7 +3844,11 @@
       <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3856,10 +3856,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>781623</v>
+        <v>781563</v>
       </c>
       <c r="R31" t="n">
-        <v>7143270</v>
+        <v>7143446</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3886,17 +3886,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>gammalt bohål i granlåga, rätt storlek för tretåig hackspett</t>
+          <t>färska hål</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3926,7 +3926,7 @@
         <v>129671647</v>
       </c>
       <c r="B32" t="n">
-        <v>82924</v>
+        <v>82925</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>129671752</v>
       </c>
       <c r="B33" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4244,10 +4244,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129670180</v>
+        <v>129671452</v>
       </c>
       <c r="B35" t="n">
-        <v>91987</v>
+        <v>98798</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4255,30 +4255,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1506</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4286,10 +4287,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>781534</v>
+        <v>781558</v>
       </c>
       <c r="R35" t="n">
-        <v>7143302</v>
+        <v>7143348</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4322,11 +4323,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>på granlåga med ullticka, kötticka och rosenticka</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4354,10 +4350,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129671452</v>
+        <v>129670180</v>
       </c>
       <c r="B36" t="n">
-        <v>98797</v>
+        <v>91988</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4365,31 +4361,30 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>1506</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4397,10 +4392,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>781558</v>
+        <v>781534</v>
       </c>
       <c r="R36" t="n">
-        <v>7143348</v>
+        <v>7143302</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4433,6 +4428,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>på granlåga med ullticka, kötticka och rosenticka</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 48749-2025 artfynd.xlsx
+++ b/artfynd/A 48749-2025 artfynd.xlsx
@@ -997,42 +997,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129671369</v>
+        <v>129671604</v>
       </c>
       <c r="B5" t="n">
-        <v>98798</v>
+        <v>57737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>781313</v>
+        <v>781583</v>
       </c>
       <c r="R5" t="n">
-        <v>7143250</v>
+        <v>7143145</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1070,17 +1070,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ca 1 x 3 meter med bladrosetter!</t>
+          <t>hack i låga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1089,7 +1089,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1108,42 +1107,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129671604</v>
+        <v>129671369</v>
       </c>
       <c r="B6" t="n">
-        <v>57737</v>
+        <v>98798</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1151,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>781583</v>
+        <v>781313</v>
       </c>
       <c r="R6" t="n">
-        <v>7143145</v>
+        <v>7143250</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,17 +1180,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>hack i låga</t>
+          <t>ca 1 x 3 meter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,6 +1199,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -4134,42 +4134,41 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129671316</v>
+        <v>129670180</v>
       </c>
       <c r="B34" t="n">
-        <v>57737</v>
+        <v>91988</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>1506</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4177,10 +4176,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>781538</v>
+        <v>781534</v>
       </c>
       <c r="R34" t="n">
-        <v>7143358</v>
+        <v>7143302</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4217,7 +4216,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>hål i högstubbe</t>
+          <t>på granlåga med ullticka, kötticka och rosenticka</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4226,6 +4225,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4244,42 +4244,42 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129671452</v>
+        <v>129671316</v>
       </c>
       <c r="B35" t="n">
-        <v>98798</v>
+        <v>57737</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4287,10 +4287,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>781558</v>
+        <v>781538</v>
       </c>
       <c r="R35" t="n">
-        <v>7143348</v>
+        <v>7143358</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4325,13 +4325,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>hål i högstubbe</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4350,10 +4354,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129670180</v>
+        <v>129671452</v>
       </c>
       <c r="B36" t="n">
-        <v>91988</v>
+        <v>98798</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4361,30 +4365,31 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1506</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4392,10 +4397,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>781534</v>
+        <v>781558</v>
       </c>
       <c r="R36" t="n">
-        <v>7143302</v>
+        <v>7143348</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4428,11 +4433,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>på granlåga med ullticka, kötticka och rosenticka</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 48749-2025 artfynd.xlsx
+++ b/artfynd/A 48749-2025 artfynd.xlsx
@@ -1548,42 +1548,41 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129671431</v>
+        <v>129671725</v>
       </c>
       <c r="B10" t="n">
-        <v>98798</v>
+        <v>91606</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1591,10 +1590,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>781554</v>
+        <v>781721</v>
       </c>
       <c r="R10" t="n">
-        <v>7143299</v>
+        <v>7143412</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1621,12 +1620,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1654,7 +1653,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129671399</v>
+        <v>129671431</v>
       </c>
       <c r="B11" t="n">
         <v>98798</v>
@@ -1688,11 +1687,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1701,10 +1696,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>781522</v>
+        <v>781554</v>
       </c>
       <c r="R11" t="n">
-        <v>7143269</v>
+        <v>7143299</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1737,11 +1732,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>med överblommad blomstängel</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1769,41 +1759,46 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129671725</v>
+        <v>129671399</v>
       </c>
       <c r="B12" t="n">
-        <v>91606</v>
+        <v>98798</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1811,10 +1806,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>781721</v>
+        <v>781522</v>
       </c>
       <c r="R12" t="n">
-        <v>7143412</v>
+        <v>7143269</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,12 +1836,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>med överblommad blomstängel</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1984,42 +1984,38 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129670107</v>
+        <v>129671776</v>
       </c>
       <c r="B14" t="n">
-        <v>57737</v>
+        <v>98798</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2027,10 +2023,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>781364</v>
+        <v>781537</v>
       </c>
       <c r="R14" t="n">
-        <v>7143210</v>
+        <v>7143351</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2057,17 +2053,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>hål i naturlig granstubbe</t>
+          <t>ca 2 x 1 m med bladrosetter</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2076,6 +2072,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2094,7 +2091,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129671776</v>
+        <v>129670096</v>
       </c>
       <c r="B15" t="n">
         <v>98798</v>
@@ -2123,7 +2120,11 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -2133,10 +2134,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>781537</v>
+        <v>781314</v>
       </c>
       <c r="R15" t="n">
-        <v>7143351</v>
+        <v>7143242</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2163,17 +2164,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ca 2 x 1 m med bladrosetter</t>
+          <t>ca 1x1 meter med bladrosetter</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2201,42 +2202,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129670096</v>
+        <v>129670107</v>
       </c>
       <c r="B16" t="n">
-        <v>98798</v>
+        <v>57737</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2244,10 +2245,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>781314</v>
+        <v>781364</v>
       </c>
       <c r="R16" t="n">
-        <v>7143242</v>
+        <v>7143210</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2284,7 +2285,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ca 1x1 meter med bladrosetter</t>
+          <t>hål i naturlig granstubbe</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2293,7 +2294,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2632,42 +2632,42 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129671522</v>
+        <v>129671688</v>
       </c>
       <c r="B20" t="n">
-        <v>57737</v>
+        <v>98798</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2675,10 +2675,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>781374</v>
+        <v>781774</v>
       </c>
       <c r="R20" t="n">
-        <v>7143326</v>
+        <v>7143251</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2705,17 +2705,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>färska hål i gran</t>
+          <t>3 x 1 meter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2724,6 +2724,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2957,41 +2958,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129671769</v>
+        <v>129671522</v>
       </c>
       <c r="B23" t="n">
-        <v>91570</v>
+        <v>57737</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2999,10 +3001,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>781492</v>
+        <v>781374</v>
       </c>
       <c r="R23" t="n">
-        <v>7143441</v>
+        <v>7143326</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3029,12 +3031,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>färska hål i gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3043,7 +3050,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3062,42 +3068,41 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129671688</v>
+        <v>129671769</v>
       </c>
       <c r="B24" t="n">
-        <v>98798</v>
+        <v>91570</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3105,10 +3110,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>781774</v>
+        <v>781492</v>
       </c>
       <c r="R24" t="n">
-        <v>7143251</v>
+        <v>7143441</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3141,11 +3146,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>3 x 1 meter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 48749-2025 artfynd.xlsx
+++ b/artfynd/A 48749-2025 artfynd.xlsx
@@ -3793,7 +3793,7 @@
         <v>0</v>
       </c>
       <c r="AE30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG30" t="b">
         <v>0</v>

--- a/artfynd/A 48749-2025 artfynd.xlsx
+++ b/artfynd/A 48749-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129671363</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -887,6 +897,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129671793</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -998,6 +1013,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670096</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1109,6 +1129,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129671369</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1214,6 +1239,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129671643</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1324,6 +1354,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670229</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1434,6 +1469,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670173</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1539,6 +1579,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129671717</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1644,6 +1689,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129671725</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1754,6 +1804,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129671437</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1859,6 +1914,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129671647</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1964,6 +2024,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129671733</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2074,6 +2139,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670180</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2179,6 +2249,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129671769</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2289,6 +2364,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670107</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2399,6 +2479,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129671307</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2509,6 +2594,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129671316</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2619,6 +2709,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129671322</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2729,6 +2824,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129671514</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2839,6 +2939,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129671522</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2949,6 +3054,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129671583</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3059,6 +3169,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129671604</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3169,6 +3284,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129671611</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3275,6 +3395,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129671632</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3386,6 +3511,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129671328</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3492,6 +3622,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129671353</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3607,6 +3742,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129671399</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3718,6 +3858,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129671422</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3824,6 +3969,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129671431</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3930,6 +4080,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129671452</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4036,6 +4191,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129671659</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4142,6 +4302,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129671679</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4253,6 +4418,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129671688</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4359,6 +4529,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129671752</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4466,8 +4641,50 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129671776</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>